--- a/EDRMS_Utilization_Report_Database_Design_v1.xlsx
+++ b/EDRMS_Utilization_Report_Database_Design_v1.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Structure" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1 UtilizationReport" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2 SiteActivity" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3 UserActivity" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="4 FilePlan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Where the values come from" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="1 UtilizationReport" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2 SiteActivity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3 UserActivity" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="4 FilePlan" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +40,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -49,6 +50,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -82,6 +88,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -95,6 +116,15 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -706,7 +736,227 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CAN WE ACTUALLY GET EVERY COLUMN?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>70 columns across four tables. 64 have a source that exists today. 6 do not, and those are shaded red on the table sheets. Nothing else is customised: every other column is either read from a system, computed from columns already present, or written by the job itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>WHERE FROM</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>COLUMNS</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>HOW THE VALUE IS OBTAINED</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>WHICH COLUMNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="62" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Read straight from public."Records" or ADBSites. Populated today for declared records; the scan supplies the same column for the rest.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>UtilizationReport.DocumentId, UtilizationReport.Title, UtilizationReport.FileType, UtilizationReport.FileCreatedDate, UtilizationReport.FolderPath, UtilizationReport.LibraryName, UtilizationReport.LibraryUrl, UtilizationReport.ListId, UtilizationReport.ItemId, UtilizationReport.SiteName, UtilizationReport.SiteUrl, UtilizationReport.CreatedDate, UtilizationReport.CreatedBy, UtilizationReport.DeclarationType, UtilizationReport.HasPhysical, UtilizationReport.EDRMSRetentionLabel, UtilizationReport.EDRMSDuration, UtilizationReport.EDRMSRetentionLabelApplied, UtilizationReport.EDRMSDueDateForDisposal, UtilizationReport.RetentionStatus, UtilizationReport.SensitivityLabelName, SiteActivity.SiteUrl, SiteActivity.SiteName, SiteActivity.ProjectEndDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="62" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Microsoft Graph</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>One API call per object. GET /sites, /sites/{id}/drives, or the driveItem itself. All verified against the 7rkd12 tenant.</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>UtilizationReport.FileSize, UtilizationReport.FileModifiedDate, UtilizationReport.LibraryLastActivityDate, UtilizationReport.SiteCreatedDate, SiteActivity.SiteCreatedDate, SiteActivity.LibraryCount, SiteActivity.StorageUsed, SiteActivity.SiteOwner</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="62" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>M365 usage report</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>getSharePointSiteUsageDetail or getSharePointActivityUserDetail. Needs Reports.Read.All.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>SiteActivity.SiteVisits7, SiteActivity.SiteVisits30, SiteActivity.SiteVisits90, SiteActivity.UniqueViewers7, SiteActivity.UniqueViewers30, SiteActivity.LastActivityDate, UserActivity.UserPrincipalName, UserActivity.DisplayName, UserActivity.LastActivityDate, UserActivity.ViewedOrEditedFileCount</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="62" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SharePoint list</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>The Retention Label Mapping list, which RAC already maintains. RISK: it is unproven whether that list identifies libraries by ListId or by name. A name would be a fragile join.</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>UtilizationReport.ADBLibraryCategory, UtilizationReport.PhysicalCounterpartRetention</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="62" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Term store</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Walk the term store through Graph. UNVERIFIED: the categories in the requirement are not in this tenant.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>FilePlan.TermId, FilePlan.TermName, FilePlan.TermSetName, FilePlan.Depth</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="62" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Derived at load</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Computed by the job from columns it already has. No new source, no extra call.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>UtilizationReport.DocumentUrl, UtilizationReport.IsDeclaredRecord, UtilizationReport.IsDeleted, SiteActivity.IsDeleted</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="62" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Job generated</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>The job writes it. Identity and run stamps.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>UtilizationReport.Id, UtilizationReport.SnapshotDate, UtilizationReport.RowLoadedDate, SiteActivity.Id, SiteActivity.SnapshotDate, SiteActivity.RowLoadedDate, UserActivity.Id, UserActivity.SnapshotDate, UserActivity.RowLoadedDate, FilePlan.Id, FilePlan.SnapshotDate, FilePlan.RowLoadedDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="62" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>NEEDS A DECISION</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Nothing supplies this. A person must provide a list, write a rule, or answer a question.</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>UtilizationReport.FormatGroup, UtilizationReport.IsEdrmsCompliant, UtilizationReport.ADBDepartmentOwner, SiteActivity.IsEdrmsCompliant, SiteActivity.ADBDepartmentOwner, FilePlan.CategoryName</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.9" customWidth="1" min="1" max="1"/>
@@ -718,96 +968,102 @@
     <col width="22.9" customWidth="1" min="7" max="7"/>
     <col width="34.4" customWidth="1" min="8" max="8"/>
     <col width="50.1" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="22.9" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="22.9" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>UTILIZATION REPORT TABLE</t>
         </is>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>One row per document held in an EDRMS compliant site, declared or not. About 3.47 million rows, replaced in full at each weekly refresh. The undeclared documents are the point: without them there is no denominator and therefore no declaration rate.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>S/N</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>RELEASE EFFECTIVE</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>DECLARATION TYPE EFFECTIVE</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>COLUMN TITLE</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>REFERENCE TABLES</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>FIELD TYPE</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>FIELD VALUES/ CHOICES</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>WHERE THE VALUE COMES FROM</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t>REMARKS</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>ADB Comments</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
@@ -817,8 +1073,8 @@
           <t>Primary key. Uniquely identifies each row of the snapshot. Regenerated on every refresh, because the whole table is replaced rather than updated in place.</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr"/>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr"/>
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>uuid</t>
         </is>
@@ -833,24 +1089,29 @@
           <t>3f2a91c4-7b18-4d0e-9a52-c6f0b81c4d2e</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="11" t="inlineStr"/>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>Job generated</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="16" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>SnapshotDate</t>
         </is>
@@ -860,8 +1121,8 @@
           <t>The date the refresh job captured this data. The same value appears on every row of a single run, and it is what the Data as of line prints at the top of every dashboard.</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr"/>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr"/>
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -876,28 +1137,33 @@
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>Job generated</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>NEW. One value per run. A dashboard is only as current as this date.</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr"/>
+      <c r="L6" s="16" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>DocumentId</t>
         </is>
@@ -907,8 +1173,8 @@
           <t>The SharePoint Document ID, meaning the identifier SharePoint assigns to a document and keeps through a rename or a move.</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr"/>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr"/>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -923,28 +1189,33 @@
           <t>1000-52341</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Nullable, which is why it is not the row identity. See ListId and ItemId.</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr"/>
+      <c r="L7" s="16" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
@@ -954,8 +1225,8 @@
           <t>The filename of the document, including its extension.</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr"/>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr"/>
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -970,24 +1241,29 @@
           <t>Board Paper Q2.pdf</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="11" t="inlineStr"/>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="16" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>DocumentUrl</t>
         </is>
@@ -997,8 +1273,8 @@
           <t>The full web address of the document, so a reader can click through from the report to the file itself.</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr"/>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr"/>
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1013,28 +1289,33 @@
           <t>https://adb.sharepoint.com/sites/edrms-cwrd/AnnualMeet/Board Paper Q2.pdf</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>Derived at load</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>NEW. Assembled at load time from SiteUrl, LibraryUrl, FolderPath and Title. Not stored anywhere today.</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr"/>
+      <c r="L9" s="16" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>FileType</t>
         </is>
@@ -1044,8 +1325,8 @@
           <t>The file extension in lower case, taken from the filename.</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr"/>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr"/>
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1060,75 +1341,85 @@
           <t>pdf</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>Flattened out of the FileMeta JSON, keeping the key name.</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr"/>
+      <c r="L10" s="16" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>FormatGroup</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>The format family the report groups by. Derived from FileType using a mapping list, so that doc and docx both count as Word.</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr"/>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr"/>
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>PDF / Word / Excel / PowerPoint / Email / Image files / Video files / All other formats</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="19" t="inlineStr">
+        <is>
+          <t>NEEDS A DECISION</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
         <is>
           <t>NEW. Derived. RAC signs off the extension to group mapping once; anything unrecognised falls into All other formats.</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr"/>
+      <c r="L11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>FileSize</t>
         </is>
@@ -1138,8 +1429,8 @@
           <t>The size of the file in bytes. Held in bytes rather than megabytes so nothing is rounded before it is totalled.</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr"/>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr"/>
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
@@ -1154,28 +1445,33 @@
           <t>2516582</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>Microsoft Graph</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>NEW KEY on FileMeta. Every storage figure depends on it. Microsoft Graph returns it on every item, so the scan gets it at no extra cost.</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr"/>
+      <c r="L12" s="16" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>FileCreatedDate</t>
         </is>
@@ -1185,8 +1481,8 @@
           <t>The date and time the file itself was created, which is not the same as the date it was declared a record.</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr"/>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr"/>
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>timestamp with time zone</t>
         </is>
@@ -1201,28 +1497,33 @@
           <t>2026-03-12 09:14:00+00</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>The date range on the Total Documents panel reads this column.</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr"/>
+      <c r="L13" s="16" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>FileModifiedDate</t>
         </is>
@@ -1232,8 +1533,8 @@
           <t>The date and time the file itself was last changed.</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr"/>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr"/>
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>timestamp with time zone</t>
         </is>
@@ -1248,28 +1549,33 @@
           <t>2026-06-04 16:02:00+00</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>Microsoft Graph</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>NEW. Named this way because ModifiedDate in Records means when the record row changed, not the file.</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr"/>
+      <c r="L14" s="16" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n">
+      <c r="A15" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>FolderPath</t>
         </is>
@@ -1279,8 +1585,8 @@
           <t>The folder path inside the library, so documents can be separated by folder within one library.</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr"/>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr"/>
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1295,24 +1601,29 @@
           <t>/2026/Q2/Board</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="11" t="inlineStr"/>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="16" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>LibraryName</t>
         </is>
@@ -1322,8 +1633,8 @@
           <t>The display name of the document library holding the file.</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr"/>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr"/>
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1338,28 +1649,33 @@
           <t>Annual Meetings</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>The deepest level of the drill down.</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr"/>
+      <c r="L16" s="16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>LibraryUrl</t>
         </is>
@@ -1369,8 +1685,8 @@
           <t>The web address of the library, for click through.</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr"/>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr"/>
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1385,24 +1701,29 @@
           <t>/sites/edrms-cwrd/AnnualMeet</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="11" t="inlineStr"/>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr"/>
+      <c r="L17" s="16" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>LibraryLastActivityDate</t>
         </is>
@@ -1412,8 +1733,8 @@
           <t>The date anything in the library last changed. Used to judge whether a library is still in use.</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr"/>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr"/>
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -1428,28 +1749,33 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>Microsoft Graph</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>NEW. Microsoft Graph returns it as lastModifiedDateTime on the drive, from the same call that supplies LibraryCount. Repeated on every document row of that library.</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr"/>
+      <c r="L18" s="16" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n">
+      <c r="A19" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>ListId</t>
         </is>
@@ -1459,8 +1785,8 @@
           <t>The GUID, meaning the system generated identifier, of the SharePoint library. Libraries can be renamed but this does not change, so every library figure groups on it.</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr"/>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr"/>
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>uuid</t>
         </is>
@@ -1475,28 +1801,33 @@
           <t>a869c724-ac4f-4144-8526-69b5aeef3a68</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Verified to match SharePoint's own list GUID, so the join to Graph is safe.</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr"/>
+      <c r="L19" s="16" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>ItemId</t>
         </is>
@@ -1506,8 +1837,8 @@
           <t>The item number SharePoint assigns within a library. Unique inside one library, not across libraries.</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr"/>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr"/>
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -1522,28 +1853,33 @@
           <t>203</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>With ListId this identifies exactly one item. Together they are the identity of a row.</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr"/>
+      <c r="L20" s="16" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n">
+      <c r="A21" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>ADBLibraryCategory</t>
         </is>
@@ -1553,12 +1889,12 @@
           <t>The category the library belongs to, used to group records by classification.</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>Retention Label Mapping list</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1573,28 +1909,33 @@
           <t>Common Document Library</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>SharePoint list</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>ADBMeta is empty. The same value is maintained today as Library Type in the Retention Label Mapping list.</t>
         </is>
       </c>
-      <c r="K21" s="11" t="inlineStr"/>
+      <c r="L21" s="16" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>SiteName</t>
         </is>
@@ -1604,12 +1945,12 @@
           <t>The display name of the SharePoint site holding the file.</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>Site Activity Table</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1624,24 +1965,29 @@
           <t>EDRMS CWRD</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr"/>
-      <c r="K22" s="11" t="inlineStr"/>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="16" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>SiteUrl</t>
         </is>
@@ -1651,12 +1997,12 @@
           <t>The web address of the site holding the file. This is the column that joins a document to its site.</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>Site Activity Table</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1671,28 +2017,33 @@
           <t>https://adb.sharepoint.com/sites/edrms-cwrd</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>The join key behind every department figure. Every existing row already carries it.</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr"/>
+      <c r="L23" s="16" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>SiteCreatedDate</t>
         </is>
@@ -1702,12 +2053,12 @@
           <t>The date the SharePoint site was created. Copied from the Site Activity Table so a document can be filtered by the age of its site without a join.</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>Site Activity Table</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -1722,130 +2073,145 @@
           <t>2026-01-18</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>Microsoft Graph</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>NEW.</t>
         </is>
       </c>
-      <c r="K24" s="11" t="inlineStr"/>
+      <c r="L24" s="16" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n">
+      <c r="A25" s="17" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>IsEdrmsCompliant</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>Whether the site holding this document is an EDRMS compliant site, meaning it has the Declare as Record button.</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="18" t="inlineStr">
         <is>
           <t>Site Activity Table</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="18" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="11" t="inlineStr">
         <is>
           <t>true / false</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I25" s="11" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J25" s="19" t="inlineStr">
+        <is>
+          <t>NEEDS A DECISION</t>
+        </is>
+      </c>
+      <c r="K25" s="11" t="inlineStr">
         <is>
           <t>NEW. Determined by whether the EDRMS app is installed on the site. Defines the population of this whole table.</t>
         </is>
       </c>
-      <c r="K25" s="11" t="inlineStr"/>
+      <c r="L25" s="18" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="17" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
         <is>
           <t>ADBDepartmentOwner</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>The department that owns the site holding this document. Inherited from the site rather than set on each document.</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="18" t="inlineStr">
         <is>
           <t>Site Activity Table</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="18" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>Values from the Department term set</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>CWRD</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J26" s="19" t="inlineStr">
+        <is>
+          <t>NEEDS A DECISION</t>
+        </is>
+      </c>
+      <c r="K26" s="11" t="inlineStr">
         <is>
           <t>GAP. The SharePoint column exists and is empty on every row. Arrives from the RAC site mapping, loaded onto the site and inherited through SiteUrl.</t>
         </is>
       </c>
-      <c r="K26" s="11" t="inlineStr"/>
+      <c r="L26" s="18" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n">
+      <c r="A27" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>IsDeclaredRecord</t>
         </is>
@@ -1855,8 +2221,8 @@
           <t>Whether this document has been formally declared a record. This is the single most important column in the report, because it separates the numerator from the denominator in every rate.</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr"/>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr"/>
+      <c r="G27" s="16" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
@@ -1871,28 +2237,33 @@
           <t>true</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>Derived at load</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>NEW but free. Derived at load: true where the document is present in Records, false where the scan found it and Records does not.</t>
         </is>
       </c>
-      <c r="K27" s="11" t="inlineStr"/>
+      <c r="L27" s="16" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="n">
+      <c r="A28" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>CreatedDate</t>
         </is>
@@ -1902,8 +2273,8 @@
           <t>The date and time the user declared the file as a record. Blank for a document that has never been declared.</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr"/>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr"/>
+      <c r="G28" s="16" t="inlineStr">
         <is>
           <t>timestamp with time zone</t>
         </is>
@@ -1918,28 +2289,33 @@
           <t>2026-03-12 09:14:00+00</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>Every declaration date filter reads this column. Not the file's own creation date.</t>
         </is>
       </c>
-      <c r="K28" s="11" t="inlineStr"/>
+      <c r="L28" s="16" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>CreatedBy</t>
         </is>
@@ -1949,8 +2325,8 @@
           <t>The User Principal Name, meaning the sign-in email address, of the person who declared the record.</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr"/>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="F29" s="16" t="inlineStr"/>
+      <c r="G29" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1965,24 +2341,29 @@
           <t>jperez@adb.org</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr"/>
-      <c r="K29" s="11" t="inlineStr"/>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr"/>
+      <c r="L29" s="16" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n">
+      <c r="A30" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>DeclarationType</t>
         </is>
@@ -1992,8 +2373,8 @@
           <t>Whether the record was declared individually or through a centralised process, held as a numeric code.</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr"/>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr"/>
+      <c r="G30" s="16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -2008,28 +2389,33 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>Deployed today as an integer. The code to label mapping needs confirming with the development team.</t>
         </is>
       </c>
-      <c r="K30" s="11" t="inlineStr"/>
+      <c r="L30" s="16" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n">
+      <c r="A31" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>HasPhysical</t>
         </is>
@@ -2039,8 +2425,8 @@
           <t>Whether a physical paper counterpart of this record exists.</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr"/>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="F31" s="16" t="inlineStr"/>
+      <c r="G31" s="16" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
@@ -2055,28 +2441,33 @@
           <t>false</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>Blank rather than false for undeclared documents, since neither answer is known for them.</t>
         </is>
       </c>
-      <c r="K31" s="11" t="inlineStr"/>
+      <c r="L31" s="16" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n">
+      <c r="A32" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>PhysicalCounterpartRetention</t>
         </is>
@@ -2086,12 +2477,12 @@
           <t>The retention that applies to the physical copy, maintained per library rather than per document.</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="16" t="inlineStr">
         <is>
           <t>Retention Label Mapping list</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G32" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -2106,24 +2497,29 @@
           <t>Long Term</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr"/>
-      <c r="K32" s="11" t="inlineStr"/>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>SharePoint list</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr"/>
+      <c r="L32" s="16" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="n">
+      <c r="A33" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>EDRMSRetentionLabel</t>
         </is>
@@ -2133,8 +2529,8 @@
           <t>The retention label applied to the file, which is what determines how long it is kept.</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr"/>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="F33" s="16" t="inlineStr"/>
+      <c r="G33" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -2149,28 +2545,33 @@
           <t>10 years after declaration</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>A record with no label has no disposal date and cannot be scheduled at all.</t>
         </is>
       </c>
-      <c r="K33" s="11" t="inlineStr"/>
+      <c r="L33" s="16" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n">
+      <c r="A34" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>EDRMSDuration</t>
         </is>
@@ -2180,8 +2581,8 @@
           <t>The length of the retention period attached to the label.</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr"/>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="F34" s="16" t="inlineStr"/>
+      <c r="G34" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -2196,28 +2597,33 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>Stored as text rather than a number so it can hold Permanent alongside 10. Cast before doing arithmetic on it.</t>
         </is>
       </c>
-      <c r="K34" s="11" t="inlineStr"/>
+      <c r="L34" s="16" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="n">
+      <c r="A35" s="15" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>EDRMSRetentionLabelApplied</t>
         </is>
@@ -2227,8 +2633,8 @@
           <t>The date and time the retention label was applied to the file.</t>
         </is>
       </c>
-      <c r="F35" s="11" t="inlineStr"/>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="F35" s="16" t="inlineStr"/>
+      <c r="G35" s="16" t="inlineStr">
         <is>
           <t>timestamp with time zone</t>
         </is>
@@ -2243,28 +2649,33 @@
           <t>2026-03-12 09:20:00+00</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>Never use this to date a declaration. A label can be applied to a document that was never declared.</t>
         </is>
       </c>
-      <c r="K35" s="11" t="inlineStr"/>
+      <c r="L35" s="16" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="n">
+      <c r="A36" s="15" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>EDRMSDueDateForDisposal</t>
         </is>
@@ -2274,8 +2685,8 @@
           <t>The date the record becomes due for disposal, computed as the label applied date plus the duration.</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr"/>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr"/>
+      <c r="G36" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -2290,28 +2701,33 @@
           <t>2036-03-12</t>
         </is>
       </c>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="J36" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>Already computed in the source database. Records due for disposal is a count over this column and needs nothing new.</t>
         </is>
       </c>
-      <c r="K36" s="11" t="inlineStr"/>
+      <c r="L36" s="16" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="n">
+      <c r="A37" s="15" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>RetentionStatus</t>
         </is>
@@ -2321,12 +2737,12 @@
           <t>The retention classification derived from the duration.</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>EDRMSMasters</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G37" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -2341,24 +2757,29 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr"/>
-      <c r="K37" s="11" t="inlineStr"/>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="16" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="n">
+      <c r="A38" s="15" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>SensitivityLabelName</t>
         </is>
@@ -2368,8 +2789,8 @@
           <t>The sensitivity label applied to the file, such as Internal or Confidential.</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr"/>
-      <c r="G38" s="11" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr"/>
+      <c r="G38" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -2384,28 +2805,33 @@
           <t>Internal</t>
         </is>
       </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>Not on any current dashboard. Carried because it is free and the obvious basis for a protection view.</t>
         </is>
       </c>
-      <c r="K38" s="11" t="inlineStr"/>
+      <c r="L38" s="16" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="n">
+      <c r="A39" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>IsDeleted</t>
         </is>
@@ -2415,8 +2841,8 @@
           <t>Soft delete flag. Every count on every dashboard excludes rows where this is true.</t>
         </is>
       </c>
-      <c r="F39" s="11" t="inlineStr"/>
-      <c r="G39" s="11" t="inlineStr">
+      <c r="F39" s="16" t="inlineStr"/>
+      <c r="G39" s="16" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
@@ -2431,28 +2857,33 @@
           <t>false</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>Derived at load</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>For undeclared documents, absence from the next scan is the delete signal.</t>
         </is>
       </c>
-      <c r="K39" s="11" t="inlineStr"/>
+      <c r="L39" s="16" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="n">
+      <c r="A40" s="15" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>RowLoadedDate</t>
         </is>
@@ -2462,8 +2893,8 @@
           <t>The date and time this row was last written by the refresh job.</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr"/>
-      <c r="G40" s="11" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr"/>
+      <c r="G40" s="16" t="inlineStr">
         <is>
           <t>timestamp with time zone</t>
         </is>
@@ -2478,29 +2909,34 @@
           <t>2026-07-27 06:00:00+00</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>Job generated</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>NEW. Operational only. Lets a failed or partial refresh be spotted.</t>
         </is>
       </c>
-      <c r="K40" s="11" t="inlineStr"/>
+      <c r="L40" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.9" customWidth="1" min="1" max="1"/>
@@ -2512,96 +2948,102 @@
     <col width="22.9" customWidth="1" min="7" max="7"/>
     <col width="34.4" customWidth="1" min="8" max="8"/>
     <col width="50.1" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="22.9" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="22.9" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>SITE ACTIVITY TABLE</t>
         </is>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>One row per SharePoint site. About 1,057 rows. Exists for the two things a document level table cannot do: count a site that holds no documents, and hold visit and viewer counts that are measured per site and would be nonsense repeated on every document row.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>S/N</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>RELEASE EFFECTIVE</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>DECLARATION TYPE EFFECTIVE</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>COLUMN TITLE</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>REFERENCE TABLES</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>FIELD TYPE</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>FIELD VALUES/ CHOICES</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>WHERE THE VALUE COMES FROM</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t>REMARKS</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>ADB Comments</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
@@ -2611,8 +3053,8 @@
           <t>Primary key. Uniquely identifies each site row of the snapshot.</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr"/>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr"/>
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>uuid</t>
         </is>
@@ -2627,24 +3069,29 @@
           <t>8c1d47b2-93ae-4f60-b1d5-2e7a6f0c9d31</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="11" t="inlineStr"/>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>Job generated</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="16" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>SnapshotDate</t>
         </is>
@@ -2654,8 +3101,8 @@
           <t>The date the refresh job captured this data. The same value on every row of a run.</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr"/>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr"/>
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -2670,28 +3117,33 @@
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>Job generated</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>NEW.</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr"/>
+      <c r="L6" s="16" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>SiteUrl</t>
         </is>
@@ -2701,12 +3153,12 @@
           <t>The web address of the site. This is the column that joins this table to the Utilization Report Table.</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Utilization Report Table</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -2721,28 +3173,33 @@
           <t>https://adb.sharepoint.com/sites/edrms-cwrd</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Ask the development team whether the site GUID is also available. A URL can change; a GUID cannot.</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr"/>
+      <c r="L7" s="16" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>SiteName</t>
         </is>
@@ -2752,8 +3209,8 @@
           <t>The display name of the site.</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr"/>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr"/>
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -2768,24 +3225,29 @@
           <t>EDRMS CWRD</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="11" t="inlineStr"/>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="16" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>SiteCreatedDate</t>
         </is>
@@ -2795,8 +3257,8 @@
           <t>The date the SharePoint site was created.</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr"/>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr"/>
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -2811,122 +3273,137 @@
           <t>2026-01-18</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>Microsoft Graph</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>NEW. Microsoft Graph returns it as createdDateTime on every site.</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr"/>
+      <c r="L9" s="16" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>IsEdrmsCompliant</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Whether this is an EDRMS compliant site, meaning the Declare as Record button is available in it.</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr"/>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr"/>
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>true / false</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="19" t="inlineStr">
+        <is>
+          <t>NEEDS A DECISION</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>NEW. Determined by whether the EDRMS app is installed on the site. Product ID {B255A2AF-7F63-4A30-966A-5D5FD99F97D7}.</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr"/>
+      <c r="L10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>ADBDepartmentOwner</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>The department that owns this site.</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr"/>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr"/>
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>Values from the Department term set</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>CWRD</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="19" t="inlineStr">
+        <is>
+          <t>NEEDS A DECISION</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
         <is>
           <t>GAP. Nothing in SharePoint supplies it. Loaded once from the RAC site mapping, roughly 1,057 rows, and inherited by every document in the site.</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr"/>
+      <c r="L11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>SiteVisits7</t>
         </is>
@@ -2936,8 +3413,8 @@
           <t>The number of page views in the site over the last 7 days.</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr"/>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr"/>
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -2952,28 +3429,33 @@
           <t>412</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>M365 usage report</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>NEW. From the Microsoft 365 SharePoint site usage report.</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr"/>
+      <c r="L12" s="16" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>SiteVisits30</t>
         </is>
@@ -2983,8 +3465,8 @@
           <t>The number of page views in the site over the last 30 days.</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr"/>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr"/>
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -2999,28 +3481,33 @@
           <t>4812</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>M365 usage report</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>NEW. Same report at period='D30'.</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr"/>
+      <c r="L13" s="16" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>SiteVisits90</t>
         </is>
@@ -3030,8 +3517,8 @@
           <t>The number of page views in the site over the last 90 days.</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr"/>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr"/>
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -3046,28 +3533,33 @@
           <t>13240</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>M365 usage report</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>NEW. Same report at period='D90'.</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr"/>
+      <c r="L14" s="16" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n">
+      <c r="A15" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>UniqueViewers7</t>
         </is>
@@ -3077,8 +3569,8 @@
           <t>The number of distinct people who opened something in the site over the last 7 days.</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr"/>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr"/>
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -3093,28 +3585,33 @@
           <t>38</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>M365 usage report</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>NEW. Do not sum this across sites to count people: anyone working in three sites is counted three times.</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr"/>
+      <c r="L15" s="16" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>UniqueViewers30</t>
         </is>
@@ -3124,8 +3621,8 @@
           <t>The number of distinct people who opened something in the site over the last 30 days.</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr"/>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr"/>
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -3140,28 +3637,33 @@
           <t>122</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>M365 usage report</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>NEW. Microsoft returns no equivalent at 90 days, which is why there is no UniqueViewers90 column.</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr"/>
+      <c r="L16" s="16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>LibraryCount</t>
         </is>
@@ -3171,8 +3673,8 @@
           <t>The number of document libraries in the site.</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr"/>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr"/>
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -3187,28 +3689,33 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>Microsoft Graph</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>NEW. Microsoft Graph, GET /sites/{id}/drives, counted.</t>
         </is>
       </c>
-      <c r="K17" s="11" t="inlineStr"/>
+      <c r="L17" s="16" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>LastActivityDate</t>
         </is>
@@ -3218,8 +3725,8 @@
           <t>The date anything in the site was last touched.</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr"/>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr"/>
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -3234,28 +3741,33 @@
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>M365 usage report</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>NEW. A site with no activity for 90 days is reported as inactive. The threshold is applied in the report, not stored here.</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr"/>
+      <c r="L18" s="16" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n">
+      <c r="A19" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>StorageUsed</t>
         </is>
@@ -3265,8 +3777,8 @@
           <t>The storage consumed by the site, in bytes.</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr"/>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr"/>
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
@@ -3281,28 +3793,33 @@
           <t>13636370432</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>Microsoft Graph</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>NEW. Includes version history, so it reads higher than the sum of FileSize. Expected, not an error.</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr"/>
+      <c r="L19" s="16" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>SiteOwner</t>
         </is>
@@ -3312,8 +3829,8 @@
           <t>The User Principal Name of the primary site administrator, meaning who to contact about a site that has gone quiet.</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr"/>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr"/>
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -3328,28 +3845,33 @@
           <t>jperez@adb.org</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>Microsoft Graph</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>NEW. Measured at 1,683 of 1,702 sites carrying one.</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr"/>
+      <c r="L20" s="16" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n">
+      <c r="A21" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>ProjectEndDate</t>
         </is>
@@ -3359,12 +3881,12 @@
           <t>The project end date recorded against the site.</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>ADBSites</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -3379,28 +3901,33 @@
           <t>2027-12-31</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Already exists and is populated. The obvious basis for a site closure view.</t>
         </is>
       </c>
-      <c r="K21" s="11" t="inlineStr"/>
+      <c r="L21" s="16" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>IsDeleted</t>
         </is>
@@ -3410,8 +3937,8 @@
           <t>Soft delete flag. Closed sites stay in the table so historical figures do not change.</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr"/>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr"/>
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
@@ -3426,28 +3953,33 @@
           <t>false</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>Derived at load</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>A site missing from the next export is the delete signal.</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr"/>
+      <c r="L22" s="16" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>RowLoadedDate</t>
         </is>
@@ -3457,8 +3989,8 @@
           <t>The date and time this row was last written.</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr"/>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr"/>
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>timestamp with time zone</t>
         </is>
@@ -3473,29 +4005,34 @@
           <t>2026-07-27 06:00:00+00</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>Job generated</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>NEW. Operational only.</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr"/>
+      <c r="L23" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.9" customWidth="1" min="1" max="1"/>
@@ -3507,96 +4044,102 @@
     <col width="22.9" customWidth="1" min="7" max="7"/>
     <col width="34.4" customWidth="1" min="8" max="8"/>
     <col width="50.1" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="22.9" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="22.9" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>USER ACTIVITY TABLE</t>
         </is>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>One row per person who used SharePoint in the window. About 9,400 rows. Exists because Total EDRMS Users counts people, and a person working in three sites appears in three rows of the Site Activity Table, so summing UniqueViewers30 overstates headcount.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>S/N</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>RELEASE EFFECTIVE</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>DECLARATION TYPE EFFECTIVE</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>COLUMN TITLE</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>REFERENCE TABLES</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>FIELD TYPE</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>FIELD VALUES/ CHOICES</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>WHERE THE VALUE COMES FROM</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t>REMARKS</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>ADB Comments</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
@@ -3606,8 +4149,8 @@
           <t>Primary key. Uniquely identifies each person row of the snapshot.</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr"/>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr"/>
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>uuid</t>
         </is>
@@ -3622,24 +4165,29 @@
           <t>b47f2e0a-5c93-41d8-8a16-7f3d05e6b8c2</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="11" t="inlineStr"/>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>Job generated</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="16" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>SnapshotDate</t>
         </is>
@@ -3649,8 +4197,8 @@
           <t>The date the refresh job captured this data.</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr"/>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr"/>
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -3665,28 +4213,33 @@
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>Job generated</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>NEW.</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr"/>
+      <c r="L6" s="16" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>UserPrincipalName</t>
         </is>
@@ -3696,8 +4249,8 @@
           <t>The User Principal Name, meaning the sign-in email address, of a person who used SharePoint in the window. Counting distinct values of this column is the entire purpose of the table.</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr"/>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr"/>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -3712,28 +4265,33 @@
           <t>jperez@adb.org</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>M365 usage report</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>NEW. This is why the table exists: people cannot be counted from a table of sites.</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr"/>
+      <c r="L7" s="16" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>DisplayName</t>
         </is>
@@ -3743,8 +4301,8 @@
           <t>The person's display name, for readability when the list is inspected.</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr"/>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr"/>
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -3759,28 +4317,33 @@
           <t>J Perez</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>M365 usage report</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>NEW.</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr"/>
+      <c r="L8" s="16" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>LastActivityDate</t>
         </is>
@@ -3790,8 +4353,8 @@
           <t>The date of the person's most recent SharePoint activity.</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr"/>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr"/>
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -3806,28 +4369,33 @@
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>M365 usage report</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>NEW. Filter on this to count active users over 7 or 30 days.</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr"/>
+      <c r="L9" s="16" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>ViewedOrEditedFileCount</t>
         </is>
@@ -3837,8 +4405,8 @@
           <t>The number of files the person viewed or edited during the window.</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr"/>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr"/>
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -3853,28 +4421,33 @@
           <t>42</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>M365 usage report</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>NEW. Separates heavy users from someone who opened one document, and is the obvious basis for an adoption view.</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr"/>
+      <c r="L10" s="16" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>RowLoadedDate</t>
         </is>
@@ -3884,8 +4457,8 @@
           <t>The date and time this row was last written.</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr"/>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr"/>
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>timestamp with time zone</t>
         </is>
@@ -3900,29 +4473,34 @@
           <t>2026-07-27 06:00:00+00</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>Job generated</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>NEW. Operational only.</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr"/>
+      <c r="L11" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.9" customWidth="1" min="1" max="1"/>
@@ -3934,96 +4512,102 @@
     <col width="22.9" customWidth="1" min="7" max="7"/>
     <col width="34.4" customWidth="1" min="8" max="8"/>
     <col width="50.1" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="22.9" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="22.9" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>FILE PLAN TABLE</t>
         </is>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>One row per term in the institutional file plan. Exists because the file plan is the taxonomy that classifies content, so its terms are neither documents nor sites nor people and none of the other three tables can hold them.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>S/N</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>RELEASE EFFECTIVE</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>DECLARATION TYPE EFFECTIVE</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>COLUMN TITLE</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>REFERENCE TABLES</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>FIELD TYPE</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>FIELD VALUES/ CHOICES</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>WHERE THE VALUE COMES FROM</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t>REMARKS</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>ADB Comments</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
@@ -4033,8 +4617,8 @@
           <t>Primary key. Uniquely identifies each term row of the snapshot.</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr"/>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr"/>
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>uuid</t>
         </is>
@@ -4049,24 +4633,29 @@
           <t>e05b8c31-7d42-4a96-b3f8-1c9e4a70d582</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="11" t="inlineStr"/>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>Job generated</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="16" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>SnapshotDate</t>
         </is>
@@ -4076,8 +4665,8 @@
           <t>The date the refresh job captured this data.</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr"/>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr"/>
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -4092,28 +4681,33 @@
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>Job generated</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>NEW.</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr"/>
+      <c r="L6" s="16" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>TermId</t>
         </is>
@@ -4123,8 +4717,8 @@
           <t>The GUID, meaning the system generated identifier, of the term. Stable across a rename, so counts do not jump when somebody edits a label.</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr"/>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr"/>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>uuid</t>
         </is>
@@ -4139,28 +4733,33 @@
           <t>6f2c1a48-9b30-4e75-8d21-c4a7e0f39a41</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>Term store</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>NEW.</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr"/>
+      <c r="L7" s="16" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>TermName</t>
         </is>
@@ -4170,8 +4769,8 @@
           <t>The label of the term as it appears in the term store.</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr"/>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr"/>
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -4186,28 +4785,33 @@
           <t>Procurement Planning</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>Term store</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>NEW.</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr"/>
+      <c r="L8" s="16" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>TermSetName</t>
         </is>
@@ -4217,8 +4821,8 @@
           <t>The term set the term belongs to.</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr"/>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr"/>
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -4233,75 +4837,85 @@
           <t>Procurement</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>Term store</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>NEW.</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr"/>
+      <c r="L9" s="16" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>CategoryName</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>The top level term group the term sits under, which is what the report groups by.</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr"/>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr"/>
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Values from the term store groups</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>ADB</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="19" t="inlineStr">
+        <is>
+          <t>NEEDS A DECISION</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>NEW. UNVERIFIED. The five categories in the requirement do not exist in the tenant's term store. See the Structure sheet.</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr"/>
+      <c r="L10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Depth</t>
         </is>
@@ -4311,8 +4925,8 @@
           <t>How many levels below the term set the term sits. A term directly under a term set is 1.</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr"/>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr"/>
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -4327,28 +4941,33 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>Term store</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>NEW. Recorded while walking the tree at no extra cost, and it answers how deep the plan actually runs.</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr"/>
+      <c r="L11" s="16" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>RowLoadedDate</t>
         </is>
@@ -4358,8 +4977,8 @@
           <t>The date and time this row was last written.</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr"/>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr"/>
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>timestamp with time zone</t>
         </is>
@@ -4374,17 +4993,22 @@
           <t>2026-07-27 06:00:00+00</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>Job generated</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>NEW. Operational only.</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr"/>
+      <c r="L12" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EDRMS_Utilization_Report_Database_Design_v1.xlsx
+++ b/EDRMS_Utilization_Report_Database_Design_v1.xlsx
@@ -736,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -828,23 +828,23 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>getSharePointSiteUsageDetail or getSharePointActivityUserDetail. Needs Reports.Read.All.</t>
+          <t>Downloadable as CSV from the Microsoft 365 admin centre, Reports, Usage. Two different reports: SharePoint site usage gives one row per site, SharePoint activity gives one row per user. Needs Reports.Read.All for the API version.</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>SiteActivity.SiteVisits7, SiteActivity.SiteVisits30, SiteActivity.SiteVisits90, SiteActivity.UniqueViewers7, SiteActivity.UniqueViewers30, SiteActivity.LastActivityDate, UserActivity.UserPrincipalName, UserActivity.DisplayName, UserActivity.LastActivityDate, UserActivity.ViewedOrEditedFileCount</t>
+          <t>SiteActivity.SiteVisits7, SiteActivity.SiteVisits30, SiteActivity.SiteVisits90, SiteActivity.LastActivityDate, UserActivity.UserPrincipalName, UserActivity.DisplayName, UserActivity.LastActivityDate, UserActivity.ViewedOrEditedFileCount</t>
         </is>
       </c>
     </row>
     <row r="8" ht="62" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SharePoint list</t>
+          <t>Site analytics</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
@@ -852,39 +852,39 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>The Retention Label Mapping list, which RAC already maintains. RISK: it is unproven whether that list identifies libraries by ListId or by name. A name would be a fragile join.</t>
+          <t>GET /sites/{id}/analytics/{window}, the actorCount field. NOT in the usage export, which carries no unique viewer column at all. Only allTime and lastSevenDays exist as windows.</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>UtilizationReport.ADBLibraryCategory, UtilizationReport.PhysicalCounterpartRetention</t>
+          <t>SiteActivity.UniqueViewers7, SiteActivity.UniqueViewersAllTime</t>
         </is>
       </c>
     </row>
     <row r="9" ht="62" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Term store</t>
+          <t>SharePoint list</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Walk the term store through Graph. UNVERIFIED: the categories in the requirement are not in this tenant.</t>
+          <t>The Retention Label Mapping list, which RAC already maintains. RISK: it is unproven whether that list identifies libraries by ListId or by name. A name would be a fragile join.</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>FilePlan.TermId, FilePlan.TermName, FilePlan.TermSetName, FilePlan.Depth</t>
+          <t>UtilizationReport.ADBLibraryCategory, UtilizationReport.PhysicalCounterpartRetention</t>
         </is>
       </c>
     </row>
     <row r="10" ht="62" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Derived at load</t>
+          <t>Term store</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
@@ -892,50 +892,70 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Computed by the job from columns it already has. No new source, no extra call.</t>
+          <t>Walk the term store through Graph. UNVERIFIED: the categories in the requirement are not in this tenant.</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>UtilizationReport.DocumentUrl, UtilizationReport.IsDeclaredRecord, UtilizationReport.IsDeleted, SiteActivity.IsDeleted</t>
+          <t>FilePlan.TermId, FilePlan.TermName, FilePlan.TermSetName, FilePlan.Depth</t>
         </is>
       </c>
     </row>
     <row r="11" ht="62" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t>Derived at load</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Computed by the job from columns it already has. No new source, no extra call.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>UtilizationReport.DocumentUrl, UtilizationReport.IsDeclaredRecord, UtilizationReport.IsDeleted, SiteActivity.IsDeleted</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="62" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>Job generated</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B12" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>The job writes it. Identity and run stamps.</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>UtilizationReport.Id, UtilizationReport.SnapshotDate, UtilizationReport.RowLoadedDate, SiteActivity.Id, SiteActivity.SnapshotDate, SiteActivity.RowLoadedDate, UserActivity.Id, UserActivity.SnapshotDate, UserActivity.RowLoadedDate, FilePlan.Id, FilePlan.SnapshotDate, FilePlan.RowLoadedDate</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="62" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="13" ht="62" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>NEEDS A DECISION</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B13" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Nothing supplies this. A person must provide a list, write a rule, or answer a question.</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>UtilizationReport.FormatGroup, UtilizationReport.IsEdrmsCompliant, UtilizationReport.ADBDepartmentOwner, SiteActivity.IsEdrmsCompliant, SiteActivity.ADBDepartmentOwner, FilePlan.CategoryName</t>
         </is>
@@ -3587,12 +3607,12 @@
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>M365 usage report</t>
+          <t>Site analytics</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>NEW. Do not sum this across sites to count people: anyone working in three sites is counted three times.</t>
+          <t>NEW. NOT in the usage export, which has no unique viewer column at all. Comes from GET /sites/{id}/analytics/lastSevenDays, the actorCount field. Do not sum across sites to count people: anyone working in three sites is counted three times.</t>
         </is>
       </c>
       <c r="L15" s="16" t="inlineStr"/>
@@ -3613,12 +3633,12 @@
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>UniqueViewers30</t>
+          <t>UniqueViewersAllTime</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>The number of distinct people who opened something in the site over the last 30 days.</t>
+          <t>The number of distinct people who have ever opened something in the site.</t>
         </is>
       </c>
       <c r="F16" s="16" t="inlineStr"/>
@@ -3639,12 +3659,12 @@
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>M365 usage report</t>
+          <t>Site analytics</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>NEW. Microsoft returns no equivalent at 90 days, which is why there is no UniqueViewers90 column.</t>
+          <t>NEW. Replaces a UniqueViewers30 column that could not be filled: site analytics offers all time and last seven days only, and there is no 30 or 90 day window. Verified against the tenant, which returned actorCount 12 for org_csd_1.4testsite.</t>
         </is>
       </c>
       <c r="L16" s="16" t="inlineStr"/>

--- a/EDRMS_Utilization_Report_Database_Design_v1.xlsx
+++ b/EDRMS_Utilization_Report_Database_Design_v1.xlsx
@@ -755,7 +755,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>70 columns across four tables. 64 have a source that exists today. 6 do not, and those are shaded red on the table sheets. Nothing else is customised: every other column is either read from a system, computed from columns already present, or written by the job itself.</t>
+          <t>71 columns across four tables. 65 have a source that exists today. 6 do not, and those are shaded red on the table sheets. Nothing else is customised: every other column is either read from a system, computed from columns already present, or written by the job itself.</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>UtilizationReport.FileSize, UtilizationReport.FileModifiedDate, UtilizationReport.LibraryLastActivityDate, UtilizationReport.SiteCreatedDate, SiteActivity.SiteCreatedDate, SiteActivity.LibraryCount, SiteActivity.StorageUsed, SiteActivity.SiteOwner</t>
+          <t>UtilizationReport.FileSize, UtilizationReport.FileModifiedDate, UtilizationReport.LibraryLastActivityDate, UtilizationReport.SiteCreatedDate, SiteActivity.SiteCreatedDate, SiteActivity.LibraryCount, UserActivity.DisplayName</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>SiteActivity.SiteVisits7, SiteActivity.SiteVisits30, SiteActivity.SiteVisits90, SiteActivity.LastActivityDate, UserActivity.UserPrincipalName, UserActivity.DisplayName, UserActivity.LastActivityDate, UserActivity.ViewedOrEditedFileCount</t>
+          <t>SiteActivity.SiteId, SiteActivity.SiteVisits7, SiteActivity.SiteVisits30, SiteActivity.SiteVisits90, SiteActivity.LastActivityDate, SiteActivity.StorageUsed, SiteActivity.SiteOwner, UserActivity.UserPrincipalName, UserActivity.LastActivityDate, UserActivity.ViewedOrEditedFileCount</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.9" customWidth="1" min="1" max="1"/>
@@ -3165,42 +3165,38 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>SiteUrl</t>
+          <t>SiteId</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>The web address of the site. This is the column that joins this table to the Utilization Report Table.</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>Utilization Report Table</t>
-        </is>
-      </c>
+          <t>The GUID, meaning the system generated identifier, of the SharePoint site. Stable across a rename, unlike the URL.</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr"/>
       <c r="G7" s="16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Absolute URL</t>
+          <t>SharePoint site GUID</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://adb.sharepoint.com/sites/edrms-cwrd</t>
+          <t>019adc9b-031d-4edc-b62f-512ed4671947</t>
         </is>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>EDRMS database</t>
+          <t>M365 usage report</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Ask the development team whether the site GUID is also available. A URL can change; a GUID cannot.</t>
+          <t>NEW. The usage export identifies sites by this and leaves Site URL blank on every row, so the refresh job must merge the export with a Graph site list to connect a GUID to a URL.</t>
         </is>
       </c>
       <c r="L7" s="16" t="inlineStr"/>
@@ -3221,15 +3217,19 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>SiteName</t>
+          <t>SiteUrl</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>The display name of the site.</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr"/>
+          <t>The web address of the site. This is the column that joins this table to the Utilization Report Table.</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>Utilization Report Table</t>
+        </is>
+      </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
           <t>text</t>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Free text</t>
+          <t>Absolute URL</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>EDRMS CWRD</t>
+          <t>https://adb.sharepoint.com/sites/edrms-cwrd</t>
         </is>
       </c>
       <c r="J8" s="16" t="inlineStr">
@@ -3250,7 +3250,11 @@
           <t>EDRMS database</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>NOT available from the usage export, where it is empty on all 2,575 rows. Comes from Microsoft Graph, matched to the export on SiteId.</t>
+        </is>
+      </c>
       <c r="L8" s="16" t="inlineStr"/>
     </row>
     <row r="9">
@@ -3269,93 +3273,89 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>SiteCreatedDate</t>
+          <t>SiteName</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>The date the SharePoint site was created.</t>
+          <t>The display name of the site.</t>
         </is>
       </c>
       <c r="F9" s="16" t="inlineStr"/>
       <c r="G9" s="16" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Free text</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>EDRMS CWRD</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr"/>
+      <c r="L9" s="16" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>SiteCreatedDate</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>The date the SharePoint site was created.</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr"/>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
           <t>date</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>System generated</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>2026-01-18</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="J10" s="16" t="inlineStr">
         <is>
           <t>Microsoft Graph</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>NEW. Microsoft Graph returns it as createdDateTime on every site.</t>
         </is>
       </c>
-      <c r="L9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>IsEdrmsCompliant</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>Whether this is an EDRMS compliant site, meaning the Declare as Record button is available in it.</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr"/>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>true / false</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="J10" s="19" t="inlineStr">
-        <is>
-          <t>NEEDS A DECISION</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>NEW. Determined by whether the EDRMS app is installed on the site. Product ID {B255A2AF-7F63-4A30-966A-5D5FD99F97D7}.</t>
-        </is>
-      </c>
-      <c r="L10" s="18" t="inlineStr"/>
+      <c r="L10" s="16" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="17" t="n">
@@ -3373,93 +3373,93 @@
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>ADBDepartmentOwner</t>
+          <t>IsEdrmsCompliant</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>The department that owns this site.</t>
+          <t>Whether this is an EDRMS compliant site, meaning the Declare as Record button is available in it.</t>
         </is>
       </c>
       <c r="F11" s="18" t="inlineStr"/>
       <c r="G11" s="18" t="inlineStr">
         <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>true / false</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="J11" s="19" t="inlineStr">
+        <is>
+          <t>NEEDS A DECISION</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>NEW. Determined by whether the EDRMS app is installed on the site. Product ID {B255A2AF-7F63-4A30-966A-5D5FD99F97D7}.</t>
+        </is>
+      </c>
+      <c r="L11" s="18" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>ADBDepartmentOwner</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>The department that owns this site.</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr"/>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
           <t>text</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>Values from the Department term set</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>CWRD</t>
         </is>
       </c>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="J12" s="19" t="inlineStr">
         <is>
           <t>NEEDS A DECISION</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr">
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>GAP. Nothing in SharePoint supplies it. Loaded once from the RAC site mapping, roughly 1,057 rows, and inherited by every document in the site.</t>
         </is>
       </c>
-      <c r="L11" s="18" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>2026.4</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>SiteVisits7</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>The number of page views in the site over the last 7 days.</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr"/>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>System generated</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>M365 usage report</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>NEW. From the Microsoft 365 SharePoint site usage report.</t>
-        </is>
-      </c>
-      <c r="L12" s="16" t="inlineStr"/>
+      <c r="L12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="15" t="n">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>SiteVisits30</t>
+          <t>SiteVisits7</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>The number of page views in the site over the last 30 days.</t>
+          <t>The number of page views in the site over the last 7 days.</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr"/>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>412</t>
         </is>
       </c>
       <c r="J13" s="16" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>NEW. Same report at period='D30'.</t>
+          <t>NEW. From the Microsoft 365 SharePoint site usage report.</t>
         </is>
       </c>
       <c r="L13" s="16" t="inlineStr"/>
@@ -3529,12 +3529,12 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>SiteVisits90</t>
+          <t>SiteVisits30</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>The number of page views in the site over the last 90 days.</t>
+          <t>The number of page views in the site over the last 30 days.</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr"/>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>13240</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="J14" s="16" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>NEW. Same report at period='D90'.</t>
+          <t>NEW. Same report at period='D30'.</t>
         </is>
       </c>
       <c r="L14" s="16" t="inlineStr"/>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>UniqueViewers7</t>
+          <t>SiteVisits90</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>The number of distinct people who opened something in the site over the last 7 days.</t>
+          <t>The number of page views in the site over the last 90 days.</t>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr"/>
@@ -3602,17 +3602,17 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>Site analytics</t>
+          <t>M365 usage report</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>NEW. NOT in the usage export, which has no unique viewer column at all. Comes from GET /sites/{id}/analytics/lastSevenDays, the actorCount field. Do not sum across sites to count people: anyone working in three sites is counted three times.</t>
+          <t>NEW. Same report at period='D90'.</t>
         </is>
       </c>
       <c r="L15" s="16" t="inlineStr"/>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>UniqueViewersAllTime</t>
+          <t>UniqueViewers7</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>The number of distinct people who have ever opened something in the site.</t>
+          <t>The number of distinct people who opened something in the site over the last 7 days.</t>
         </is>
       </c>
       <c r="F16" s="16" t="inlineStr"/>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J16" s="16" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>NEW. Replaces a UniqueViewers30 column that could not be filled: site analytics offers all time and last seven days only, and there is no 30 or 90 day window. Verified against the tenant, which returned actorCount 12 for org_csd_1.4testsite.</t>
+          <t>NEW. NOT in the usage export, which has no unique viewer column at all. Comes from GET /sites/{id}/analytics/lastSevenDays, the actorCount field. Do not sum across sites to count people: anyone working in three sites is counted three times.</t>
         </is>
       </c>
       <c r="L16" s="16" t="inlineStr"/>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>LibraryCount</t>
+          <t>UniqueViewersAllTime</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>The number of document libraries in the site.</t>
+          <t>The number of distinct people who have ever opened something in the site.</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr"/>
@@ -3706,17 +3706,17 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>122</t>
         </is>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>Microsoft Graph</t>
+          <t>Site analytics</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>NEW. Microsoft Graph, GET /sites/{id}/drives, counted.</t>
+          <t>NEW. Replaces a UniqueViewers30 column that could not be filled: site analytics offers all time and last seven days only, and there is no 30 or 90 day window. Verified against the tenant, which returned actorCount 12 for org_csd_1.4testsite.</t>
         </is>
       </c>
       <c r="L17" s="16" t="inlineStr"/>
@@ -3737,18 +3737,18 @@
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>LastActivityDate</t>
+          <t>LibraryCount</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>The date anything in the site was last touched.</t>
+          <t>The number of document libraries in the site.</t>
         </is>
       </c>
       <c r="F18" s="16" t="inlineStr"/>
       <c r="G18" s="16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -3758,17 +3758,17 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>M365 usage report</t>
+          <t>Microsoft Graph</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>NEW. A site with no activity for 90 days is reported as inactive. The threshold is applied in the report, not stored here.</t>
+          <t>NEW. Microsoft Graph, GET /sites/{id}/drives, counted.</t>
         </is>
       </c>
       <c r="L18" s="16" t="inlineStr"/>
@@ -3789,18 +3789,18 @@
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>StorageUsed</t>
+          <t>LastActivityDate</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>The storage consumed by the site, in bytes.</t>
+          <t>The date anything in the site was last touched.</t>
         </is>
       </c>
       <c r="F19" s="16" t="inlineStr"/>
       <c r="G19" s="16" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>date</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -3810,17 +3810,17 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>13636370432</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>Microsoft Graph</t>
+          <t>M365 usage report</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>NEW. Includes version history, so it reads higher than the sum of FileSize. Expected, not an error.</t>
+          <t>NEW. A site with no activity for 90 days is reported as inactive. The threshold is applied in the report, not stored here.</t>
         </is>
       </c>
       <c r="L19" s="16" t="inlineStr"/>
@@ -3841,38 +3841,38 @@
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>SiteOwner</t>
+          <t>StorageUsed</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>The User Principal Name of the primary site administrator, meaning who to contact about a site that has gone quiet.</t>
+          <t>The storage consumed by the site, in bytes.</t>
         </is>
       </c>
       <c r="F20" s="16" t="inlineStr"/>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Valid ADB UPN</t>
+          <t>System generated</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>jperez@adb.org</t>
+          <t>13636370432</t>
         </is>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>Microsoft Graph</t>
+          <t>M365 usage report</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>NEW. Measured at 1,683 of 1,702 sites carrying one.</t>
+          <t>NEW. Includes version history, so it reads higher than the sum of FileSize. Expected, not an error.</t>
         </is>
       </c>
       <c r="L20" s="16" t="inlineStr"/>
@@ -3893,42 +3893,38 @@
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>ProjectEndDate</t>
+          <t>SiteOwner</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>The project end date recorded against the site.</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>ADBSites</t>
-        </is>
-      </c>
+          <t>The User Principal Name of the primary site administrator, meaning who to contact about a site that has gone quiet.</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr"/>
       <c r="G21" s="16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>System generated</t>
+          <t>Valid ADB UPN</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>jperez@adb.org</t>
         </is>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>EDRMS database</t>
+          <t>M365 usage report</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Already exists and is populated. The obvious basis for a site closure view.</t>
+          <t>NEW. Usage export, Owner Principal Name. Verified: 1,899 of 1,918 live sites carry one, so 19 have no owner at all.</t>
         </is>
       </c>
       <c r="L21" s="16" t="inlineStr"/>
@@ -3949,38 +3945,42 @@
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>IsDeleted</t>
+          <t>ProjectEndDate</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Soft delete flag. Closed sites stay in the table so historical figures do not change.</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr"/>
+          <t>The project end date recorded against the site.</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>ADBSites</t>
+        </is>
+      </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>date</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>true / false</t>
+          <t>System generated</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>2027-12-31</t>
         </is>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>Derived at load</t>
+          <t>EDRMS database</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>A site missing from the next export is the delete signal.</t>
+          <t>Already exists and is populated. The obvious basis for a site closure view.</t>
         </is>
       </c>
       <c r="L22" s="16" t="inlineStr"/>
@@ -4001,41 +4001,93 @@
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>RowLoadedDate</t>
+          <t>IsDeleted</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>The date and time this row was last written.</t>
+          <t>Soft delete flag. Closed sites stay in the table so historical figures do not change.</t>
         </is>
       </c>
       <c r="F23" s="16" t="inlineStr"/>
       <c r="G23" s="16" t="inlineStr">
         <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>true / false</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>Derived at load</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>A site missing from the next export is the delete signal.</t>
+        </is>
+      </c>
+      <c r="L23" s="16" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>RowLoadedDate</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>The date and time this row was last written.</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr"/>
+      <c r="G24" s="16" t="inlineStr">
+        <is>
           <t>timestamp with time zone</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>System generated</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>2026-07-27 06:00:00+00</t>
         </is>
       </c>
-      <c r="J23" s="16" t="inlineStr">
+      <c r="J24" s="16" t="inlineStr">
         <is>
           <t>Job generated</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>NEW. Operational only.</t>
         </is>
       </c>
-      <c r="L23" s="16" t="inlineStr"/>
+      <c r="L24" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4292,7 +4344,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>NEW. This is why the table exists: people cannot be counted from a table of sites.</t>
+          <t>NEW. This is why the table exists: people cannot be counted from a table of sites. **Monthly active users is NOT the row count**: the export lists every licensed user, active or not. Verified on the tenant, where 30 rows held only 8 people who viewed or edited anything. Count rows where ViewedOrEditedFileCount is above zero.</t>
         </is>
       </c>
       <c r="L7" s="16" t="inlineStr"/>
@@ -4339,12 +4391,12 @@
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>M365 usage report</t>
+          <t>Microsoft Graph</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>NEW.</t>
+          <t>NEW. NOT in the activity export, which carries User Principal Name and no display name. Needs a separate Graph call to /users, and it is cosmetic, so drop it if that call is not worth making.</t>
         </is>
       </c>
       <c r="L8" s="16" t="inlineStr"/>

--- a/EDRMS_Utilization_Report_Database_Design_v1.xlsx
+++ b/EDRMS_Utilization_Report_Database_Design_v1.xlsx
@@ -9,10 +9,11 @@
   <sheets>
     <sheet name="Structure" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Where the values come from" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="1 UtilizationReport" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2 SiteActivity" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="3 UserActivity" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="4 FilePlan" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Verification tracker" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1 UtilizationReport" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2 SiteActivity" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="3 UserActivity" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="4 FilePlan" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40,7 +41,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +58,11 @@
         <fgColor rgb="FFFBE4E4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F4EC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -70,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -103,12 +109,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -123,6 +123,24 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -976,6 +994,2388 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>VERIFICATION TRACKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Every column in the design, with the table it belongs to. EXACT SOURCE FIELD and EVIDENCE are filled only where there is proof. Everything else is blank on purpose: writing an expectation into the source column would be indistinguishable from a verified fact in three weeks. Fill YOUR FINDING as you test, and where it disagrees with the WHERE TO LOOK column, the expectation was wrong. That is how three errors were caught on 12 August.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>DATABASE TABLE</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>COLUMN NAME</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>FIELD TYPE</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>WHERE TO LOOK (my expectation, unverified)</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>EXACT SOURCE FIELD (confirmed only)</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>EVIDENCE</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>YOUR FINDING</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>DATE TESTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to test. Written by the job</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr"/>
+      <c r="G5" s="13" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="13" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>SnapshotDate</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to test. Written by the job</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr"/>
+      <c r="G6" s="13" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="13" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>DocumentId</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="13" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="13" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr"/>
+      <c r="G8" s="13" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="13" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>DocumentUrl</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to test. Computed by the job</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr"/>
+      <c r="G9" s="13" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>FileType</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr"/>
+      <c r="G10" s="13" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="13" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>FormatGroup</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Nothing to test. Somebody must supply a list or write a rule</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr"/>
+      <c r="G11" s="15" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr"/>
+      <c r="I11" s="11" t="inlineStr"/>
+      <c r="J11" s="15" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>FileSize</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>A Graph call. See the REMARKS column on the table sheet</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12" s="19" t="inlineStr">
+        <is>
+          <t>Graph returns size on every driveItem. Verified 1,506 to 2,338,767 bytes</t>
+        </is>
+      </c>
+      <c r="I12" s="19" t="inlineStr"/>
+      <c r="J12" s="17" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>FileCreatedDate</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>timestamp with time zone</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr"/>
+      <c r="G13" s="13" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>FileModifiedDate</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>timestamp with time zone</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>A Graph call. See the REMARKS column on the table sheet</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr"/>
+      <c r="G14" s="13" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="13" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>FolderPath</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr"/>
+      <c r="G15" s="13" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>LibraryName</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr"/>
+      <c r="G16" s="13" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr"/>
+      <c r="J16" s="13" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>LibraryUrl</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr"/>
+      <c r="G17" s="13" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="13" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>LibraryLastActivityDate</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>A Graph call. See the REMARKS column on the table sheet</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr"/>
+      <c r="G18" s="13" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr"/>
+      <c r="J18" s="13" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>ListId</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr"/>
+      <c r="G19" s="13" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="13" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>ItemId</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr"/>
+      <c r="G20" s="13" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="13" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>ADBLibraryCategory</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Retention Label Mapping list in app_edrms_data_uat</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr"/>
+      <c r="G21" s="13" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="13" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>SiteName</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr"/>
+      <c r="G22" s="13" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" s="13" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>SiteUrl</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr"/>
+      <c r="G23" s="13" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
+      <c r="J23" s="13" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>SiteCreatedDate</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>A Graph call. See the REMARKS column on the table sheet</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr"/>
+      <c r="G24" s="13" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="13" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>IsEdrmsCompliant</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Nothing to test. Somebody must supply a list or write a rule</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr"/>
+      <c r="G25" s="15" t="inlineStr"/>
+      <c r="H25" s="11" t="inlineStr"/>
+      <c r="I25" s="11" t="inlineStr"/>
+      <c r="J25" s="15" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>ADBDepartmentOwner</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Nothing to test. Somebody must supply a list or write a rule</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr"/>
+      <c r="G26" s="15" t="inlineStr"/>
+      <c r="H26" s="11" t="inlineStr"/>
+      <c r="I26" s="11" t="inlineStr"/>
+      <c r="J26" s="15" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>IsDeclaredRecord</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to test. Computed by the job</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr"/>
+      <c r="G27" s="13" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr"/>
+      <c r="J27" s="13" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>CreatedDate</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>timestamp with time zone</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr"/>
+      <c r="G28" s="13" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="4" t="inlineStr"/>
+      <c r="J28" s="13" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>CreatedBy</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr"/>
+      <c r="G29" s="13" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr"/>
+      <c r="J29" s="13" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>DeclarationType</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr"/>
+      <c r="G30" s="13" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr"/>
+      <c r="J30" s="13" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>HasPhysical</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr"/>
+      <c r="G31" s="13" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr"/>
+      <c r="J31" s="13" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>PhysicalCounterpartRetention</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Retention Label Mapping list in app_edrms_data_uat</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr"/>
+      <c r="G32" s="13" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr"/>
+      <c r="J32" s="13" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>EDRMSRetentionLabel</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr"/>
+      <c r="G33" s="13" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="13" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>EDRMSDuration</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr"/>
+      <c r="G34" s="13" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr"/>
+      <c r="J34" s="13" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>EDRMSRetentionLabelApplied</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>timestamp with time zone</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr"/>
+      <c r="G35" s="13" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr"/>
+      <c r="J35" s="13" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>EDRMSDueDateForDisposal</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr"/>
+      <c r="G36" s="13" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr"/>
+      <c r="J36" s="13" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>RetentionStatus</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr"/>
+      <c r="G37" s="13" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr"/>
+      <c r="J37" s="13" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>SensitivityLabelName</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr"/>
+      <c r="G38" s="13" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr"/>
+      <c r="J38" s="13" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>IsDeleted</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to test. Computed by the job</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr"/>
+      <c r="G39" s="13" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr"/>
+      <c r="J39" s="13" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>UtilizationReport</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>RowLoadedDate</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>timestamp with time zone</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to test. Written by the job</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr"/>
+      <c r="G40" s="13" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr"/>
+      <c r="J40" s="13" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to test. Written by the job</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr"/>
+      <c r="G41" s="13" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr"/>
+      <c r="J41" s="13" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>SnapshotDate</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to test. Written by the job</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr"/>
+      <c r="G42" s="13" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="13" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>SiteId</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>One of the two usage CSVs</t>
+        </is>
+      </c>
+      <c r="F43" s="18" t="inlineStr">
+        <is>
+          <t>Site Id</t>
+        </is>
+      </c>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H43" s="19" t="inlineStr">
+        <is>
+          <t>Site usage CSV, 12 Aug 2026. Populated on all 2,575 rows</t>
+        </is>
+      </c>
+      <c r="I43" s="19" t="inlineStr"/>
+      <c r="J43" s="17" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>SiteUrl</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr"/>
+      <c r="G44" s="13" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="inlineStr"/>
+      <c r="J44" s="13" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>SiteName</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr"/>
+      <c r="G45" s="13" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr"/>
+      <c r="J45" s="13" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>SiteCreatedDate</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E46" s="19" t="inlineStr">
+        <is>
+          <t>A Graph call. See the REMARKS column on the table sheet</t>
+        </is>
+      </c>
+      <c r="F46" s="18" t="inlineStr">
+        <is>
+          <t>createdDateTime</t>
+        </is>
+      </c>
+      <c r="G46" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H46" s="19" t="inlineStr">
+        <is>
+          <t>GET /sites?search=* returns it on every site</t>
+        </is>
+      </c>
+      <c r="I46" s="19" t="inlineStr"/>
+      <c r="J46" s="17" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>IsEdrmsCompliant</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>Nothing to test. Somebody must supply a list or write a rule</t>
+        </is>
+      </c>
+      <c r="F47" s="16" t="inlineStr"/>
+      <c r="G47" s="15" t="inlineStr"/>
+      <c r="H47" s="11" t="inlineStr"/>
+      <c r="I47" s="11" t="inlineStr"/>
+      <c r="J47" s="15" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>ADBDepartmentOwner</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>Nothing to test. Somebody must supply a list or write a rule</t>
+        </is>
+      </c>
+      <c r="F48" s="16" t="inlineStr"/>
+      <c r="G48" s="15" t="inlineStr"/>
+      <c r="H48" s="11" t="inlineStr"/>
+      <c r="I48" s="11" t="inlineStr"/>
+      <c r="J48" s="15" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>SiteVisits7</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>One of the two usage CSVs</t>
+        </is>
+      </c>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>Page View Count</t>
+        </is>
+      </c>
+      <c r="G49" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H49" s="19" t="inlineStr">
+        <is>
+          <t>Site usage CSV at period D7</t>
+        </is>
+      </c>
+      <c r="I49" s="19" t="inlineStr"/>
+      <c r="J49" s="17" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>SiteVisits30</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E50" s="19" t="inlineStr">
+        <is>
+          <t>One of the two usage CSVs</t>
+        </is>
+      </c>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>Page View Count</t>
+        </is>
+      </c>
+      <c r="G50" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H50" s="19" t="inlineStr">
+        <is>
+          <t>Site usage CSV, 12 Aug 2026, period 30</t>
+        </is>
+      </c>
+      <c r="I50" s="19" t="inlineStr"/>
+      <c r="J50" s="17" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>SiteVisits90</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>One of the two usage CSVs</t>
+        </is>
+      </c>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>Page View Count</t>
+        </is>
+      </c>
+      <c r="G51" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H51" s="19" t="inlineStr">
+        <is>
+          <t>Site usage CSV at period D90</t>
+        </is>
+      </c>
+      <c r="I51" s="19" t="inlineStr"/>
+      <c r="J51" s="17" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>UniqueViewers7</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>GET /sites/{id}/analytics/{allTime|lastSevenDays}</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr"/>
+      <c r="G52" s="13" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" s="4" t="inlineStr"/>
+      <c r="J52" s="13" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>UniqueViewersAllTime</t>
+        </is>
+      </c>
+      <c r="D53" s="18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E53" s="19" t="inlineStr">
+        <is>
+          <t>GET /sites/{id}/analytics/{allTime|lastSevenDays}</t>
+        </is>
+      </c>
+      <c r="F53" s="18" t="inlineStr">
+        <is>
+          <t>actorCount</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H53" s="19" t="inlineStr">
+        <is>
+          <t>GET /sites/{id}/analytics/allTime returned actorCount 12</t>
+        </is>
+      </c>
+      <c r="I53" s="19" t="inlineStr"/>
+      <c r="J53" s="17" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>LibraryCount</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>A Graph call. See the REMARKS column on the table sheet</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="inlineStr"/>
+      <c r="G54" s="13" t="inlineStr"/>
+      <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="inlineStr"/>
+      <c r="J54" s="13" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="18" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>LastActivityDate</t>
+        </is>
+      </c>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E55" s="19" t="inlineStr">
+        <is>
+          <t>One of the two usage CSVs</t>
+        </is>
+      </c>
+      <c r="F55" s="18" t="inlineStr">
+        <is>
+          <t>Last Activity Date</t>
+        </is>
+      </c>
+      <c r="G55" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H55" s="19" t="inlineStr">
+        <is>
+          <t>Site usage CSV. 381 of 1,918 live sites carry one</t>
+        </is>
+      </c>
+      <c r="I55" s="19" t="inlineStr"/>
+      <c r="J55" s="17" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>StorageUsed</t>
+        </is>
+      </c>
+      <c r="D56" s="18" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="E56" s="19" t="inlineStr">
+        <is>
+          <t>One of the two usage CSVs</t>
+        </is>
+      </c>
+      <c r="F56" s="18" t="inlineStr">
+        <is>
+          <t>Storage Used (Byte)</t>
+        </is>
+      </c>
+      <c r="G56" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H56" s="19" t="inlineStr">
+        <is>
+          <t>Site usage CSV. Sums to 142.4 GB</t>
+        </is>
+      </c>
+      <c r="I56" s="19" t="inlineStr"/>
+      <c r="J56" s="17" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="18" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>SiteOwner</t>
+        </is>
+      </c>
+      <c r="D57" s="18" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E57" s="19" t="inlineStr">
+        <is>
+          <t>One of the two usage CSVs</t>
+        </is>
+      </c>
+      <c r="F57" s="18" t="inlineStr">
+        <is>
+          <t>Owner Principal Name</t>
+        </is>
+      </c>
+      <c r="G57" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H57" s="19" t="inlineStr">
+        <is>
+          <t>Site usage CSV. 1,899 of 1,918 have one, 19 do not</t>
+        </is>
+      </c>
+      <c r="I57" s="19" t="inlineStr"/>
+      <c r="J57" s="17" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>ProjectEndDate</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr"/>
+      <c r="G58" s="13" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="13" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>IsDeleted</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to test. Computed by the job</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr"/>
+      <c r="G59" s="13" t="inlineStr"/>
+      <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" s="4" t="inlineStr"/>
+      <c r="J59" s="13" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>RowLoadedDate</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>timestamp with time zone</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to test. Written by the job</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr"/>
+      <c r="G60" s="13" t="inlineStr"/>
+      <c r="H60" s="4" t="inlineStr"/>
+      <c r="I60" s="4" t="inlineStr"/>
+      <c r="J60" s="13" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>UserActivity</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to test. Written by the job</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr"/>
+      <c r="G61" s="13" t="inlineStr"/>
+      <c r="H61" s="4" t="inlineStr"/>
+      <c r="I61" s="4" t="inlineStr"/>
+      <c r="J61" s="13" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>UserActivity</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>SnapshotDate</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to test. Written by the job</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="inlineStr"/>
+      <c r="G62" s="13" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr"/>
+      <c r="I62" s="4" t="inlineStr"/>
+      <c r="J62" s="13" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>UserActivity</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="inlineStr">
+        <is>
+          <t>UserPrincipalName</t>
+        </is>
+      </c>
+      <c r="D63" s="18" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E63" s="19" t="inlineStr">
+        <is>
+          <t>One of the two usage CSVs</t>
+        </is>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>User Principal Name</t>
+        </is>
+      </c>
+      <c r="G63" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H63" s="19" t="inlineStr">
+        <is>
+          <t>Activity CSV, 12 Aug 2026, 30 rows</t>
+        </is>
+      </c>
+      <c r="I63" s="19" t="inlineStr"/>
+      <c r="J63" s="17" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>UserActivity</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>A Graph call. See the REMARKS column on the table sheet</t>
+        </is>
+      </c>
+      <c r="F64" s="14" t="inlineStr"/>
+      <c r="G64" s="13" t="inlineStr"/>
+      <c r="H64" s="4" t="inlineStr"/>
+      <c r="I64" s="4" t="inlineStr"/>
+      <c r="J64" s="13" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="18" t="inlineStr">
+        <is>
+          <t>UserActivity</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="inlineStr">
+        <is>
+          <t>LastActivityDate</t>
+        </is>
+      </c>
+      <c r="D65" s="18" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E65" s="19" t="inlineStr">
+        <is>
+          <t>One of the two usage CSVs</t>
+        </is>
+      </c>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>Last Activity Date</t>
+        </is>
+      </c>
+      <c r="G65" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H65" s="19" t="inlineStr">
+        <is>
+          <t>Activity CSV. 25 of 30 rows carry one</t>
+        </is>
+      </c>
+      <c r="I65" s="19" t="inlineStr"/>
+      <c r="J65" s="17" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>UserActivity</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>ViewedOrEditedFileCount</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E66" s="19" t="inlineStr">
+        <is>
+          <t>One of the two usage CSVs</t>
+        </is>
+      </c>
+      <c r="F66" s="18" t="inlineStr">
+        <is>
+          <t>Viewed Or Edited File Count</t>
+        </is>
+      </c>
+      <c r="G66" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H66" s="19" t="inlineStr">
+        <is>
+          <t>Activity CSV. Only 8 of 30 are above zero, which is the real active user count</t>
+        </is>
+      </c>
+      <c r="I66" s="19" t="inlineStr"/>
+      <c r="J66" s="17" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>UserActivity</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>RowLoadedDate</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>timestamp with time zone</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to test. Written by the job</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="inlineStr"/>
+      <c r="G67" s="13" t="inlineStr"/>
+      <c r="H67" s="4" t="inlineStr"/>
+      <c r="I67" s="4" t="inlineStr"/>
+      <c r="J67" s="13" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>FilePlan</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to test. Written by the job</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="inlineStr"/>
+      <c r="G68" s="13" t="inlineStr"/>
+      <c r="H68" s="4" t="inlineStr"/>
+      <c r="I68" s="4" t="inlineStr"/>
+      <c r="J68" s="13" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>FilePlan</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>SnapshotDate</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to test. Written by the job</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr"/>
+      <c r="G69" s="13" t="inlineStr"/>
+      <c r="H69" s="4" t="inlineStr"/>
+      <c r="I69" s="4" t="inlineStr"/>
+      <c r="J69" s="13" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>FilePlan</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>TermId</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>SharePoint admin centre, Content services, Term store</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="inlineStr"/>
+      <c r="G70" s="13" t="inlineStr"/>
+      <c r="H70" s="4" t="inlineStr"/>
+      <c r="I70" s="4" t="inlineStr"/>
+      <c r="J70" s="13" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>FilePlan</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>TermName</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>SharePoint admin centre, Content services, Term store</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="inlineStr"/>
+      <c r="G71" s="13" t="inlineStr"/>
+      <c r="H71" s="4" t="inlineStr"/>
+      <c r="I71" s="4" t="inlineStr"/>
+      <c r="J71" s="13" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>FilePlan</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>TermSetName</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>SharePoint admin centre, Content services, Term store</t>
+        </is>
+      </c>
+      <c r="F72" s="14" t="inlineStr"/>
+      <c r="G72" s="13" t="inlineStr"/>
+      <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr"/>
+      <c r="J72" s="13" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="16" t="inlineStr">
+        <is>
+          <t>FilePlan</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="inlineStr">
+        <is>
+          <t>CategoryName</t>
+        </is>
+      </c>
+      <c r="D73" s="16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>Nothing to test. Somebody must supply a list or write a rule</t>
+        </is>
+      </c>
+      <c r="F73" s="16" t="inlineStr"/>
+      <c r="G73" s="15" t="inlineStr"/>
+      <c r="H73" s="11" t="inlineStr"/>
+      <c r="I73" s="11" t="inlineStr"/>
+      <c r="J73" s="15" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>FilePlan</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>Depth</t>
+        </is>
+      </c>
+      <c r="D74" s="14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>SharePoint admin centre, Content services, Term store</t>
+        </is>
+      </c>
+      <c r="F74" s="14" t="inlineStr"/>
+      <c r="G74" s="13" t="inlineStr"/>
+      <c r="H74" s="4" t="inlineStr"/>
+      <c r="I74" s="4" t="inlineStr"/>
+      <c r="J74" s="13" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>FilePlan</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>RowLoadedDate</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>timestamp with time zone</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to test. Written by the job</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr"/>
+      <c r="G75" s="13" t="inlineStr"/>
+      <c r="H75" s="4" t="inlineStr"/>
+      <c r="I75" s="4" t="inlineStr"/>
+      <c r="J75" s="13" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -994,96 +3394,96 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>UTILIZATION REPORT TABLE</t>
         </is>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>One row per document held in an EDRMS compliant site, declared or not. About 3.47 million rows, replaced in full at each weekly refresh. The undeclared documents are the point: without them there is no denominator and therefore no declaration rate.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>S/N</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>RELEASE EFFECTIVE</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>DECLARATION TYPE EFFECTIVE</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>COLUMN TITLE</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>REFERENCE TABLES</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>FIELD TYPE</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>FIELD VALUES/ CHOICES</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>WHERE THE VALUE COMES FROM</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="12" t="inlineStr">
         <is>
           <t>REMARKS</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>ADB Comments</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n">
+      <c r="A5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
@@ -1093,8 +3493,8 @@
           <t>Primary key. Uniquely identifies each row of the snapshot. Regenerated on every refresh, because the whole table is replaced rather than updated in place.</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr"/>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr"/>
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>uuid</t>
         </is>
@@ -1109,29 +3509,29 @@
           <t>3f2a91c4-7b18-4d0e-9a52-c6f0b81c4d2e</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>Job generated</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="16" t="inlineStr"/>
+      <c r="L5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>SnapshotDate</t>
         </is>
@@ -1141,8 +3541,8 @@
           <t>The date the refresh job captured this data. The same value appears on every row of a single run, and it is what the Data as of line prints at the top of every dashboard.</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr"/>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr"/>
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -1157,7 +3557,7 @@
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>Job generated</t>
         </is>
@@ -1167,23 +3567,23 @@
           <t>NEW. One value per run. A dashboard is only as current as this date.</t>
         </is>
       </c>
-      <c r="L6" s="16" t="inlineStr"/>
+      <c r="L6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>DocumentId</t>
         </is>
@@ -1193,8 +3593,8 @@
           <t>The SharePoint Document ID, meaning the identifier SharePoint assigns to a document and keeps through a rename or a move.</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1209,7 +3609,7 @@
           <t>1000-52341</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
@@ -1219,23 +3619,23 @@
           <t>Nullable, which is why it is not the row identity. See ListId and ItemId.</t>
         </is>
       </c>
-      <c r="L7" s="16" t="inlineStr"/>
+      <c r="L7" s="14" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
@@ -1245,8 +3645,8 @@
           <t>The filename of the document, including its extension.</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr"/>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr"/>
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1261,29 +3661,29 @@
           <t>Board Paper Q2.pdf</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="16" t="inlineStr"/>
+      <c r="L8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>DocumentUrl</t>
         </is>
@@ -1293,8 +3693,8 @@
           <t>The full web address of the document, so a reader can click through from the report to the file itself.</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr"/>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr"/>
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1309,7 +3709,7 @@
           <t>https://adb.sharepoint.com/sites/edrms-cwrd/AnnualMeet/Board Paper Q2.pdf</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>Derived at load</t>
         </is>
@@ -1319,23 +3719,23 @@
           <t>NEW. Assembled at load time from SiteUrl, LibraryUrl, FolderPath and Title. Not stored anywhere today.</t>
         </is>
       </c>
-      <c r="L9" s="16" t="inlineStr"/>
+      <c r="L9" s="14" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n">
+      <c r="A10" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>FileType</t>
         </is>
@@ -1345,8 +3745,8 @@
           <t>The file extension in lower case, taken from the filename.</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr"/>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr"/>
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1361,7 +3761,7 @@
           <t>pdf</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
@@ -1371,23 +3771,23 @@
           <t>Flattened out of the FileMeta JSON, keeping the key name.</t>
         </is>
       </c>
-      <c r="L10" s="16" t="inlineStr"/>
+      <c r="L10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n">
+      <c r="A11" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>FormatGroup</t>
         </is>
@@ -1397,8 +3797,8 @@
           <t>The format family the report groups by. Derived from FileType using a mapping list, so that doc and docx both count as Word.</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr"/>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr"/>
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1413,7 +3813,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t>NEEDS A DECISION</t>
         </is>
@@ -1423,23 +3823,23 @@
           <t>NEW. Derived. RAC signs off the extension to group mapping once; anything unrecognised falls into All other formats.</t>
         </is>
       </c>
-      <c r="L11" s="18" t="inlineStr"/>
+      <c r="L11" s="16" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>FileSize</t>
         </is>
@@ -1449,8 +3849,8 @@
           <t>The size of the file in bytes. Held in bytes rather than megabytes so nothing is rounded before it is totalled.</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr"/>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr"/>
+      <c r="G12" s="14" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
@@ -1465,7 +3865,7 @@
           <t>2516582</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>Microsoft Graph</t>
         </is>
@@ -1475,23 +3875,23 @@
           <t>NEW KEY on FileMeta. Every storage figure depends on it. Microsoft Graph returns it on every item, so the scan gets it at no extra cost.</t>
         </is>
       </c>
-      <c r="L12" s="16" t="inlineStr"/>
+      <c r="L12" s="14" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>FileCreatedDate</t>
         </is>
@@ -1501,8 +3901,8 @@
           <t>The date and time the file itself was created, which is not the same as the date it was declared a record.</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr"/>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr"/>
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>timestamp with time zone</t>
         </is>
@@ -1517,7 +3917,7 @@
           <t>2026-03-12 09:14:00+00</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="J13" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
@@ -1527,23 +3927,23 @@
           <t>The date range on the Total Documents panel reads this column.</t>
         </is>
       </c>
-      <c r="L13" s="16" t="inlineStr"/>
+      <c r="L13" s="14" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n">
+      <c r="A14" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>FileModifiedDate</t>
         </is>
@@ -1553,8 +3953,8 @@
           <t>The date and time the file itself was last changed.</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr"/>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr"/>
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>timestamp with time zone</t>
         </is>
@@ -1569,7 +3969,7 @@
           <t>2026-06-04 16:02:00+00</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="J14" s="14" t="inlineStr">
         <is>
           <t>Microsoft Graph</t>
         </is>
@@ -1579,23 +3979,23 @@
           <t>NEW. Named this way because ModifiedDate in Records means when the record row changed, not the file.</t>
         </is>
       </c>
-      <c r="L14" s="16" t="inlineStr"/>
+      <c r="L14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n">
+      <c r="A15" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>FolderPath</t>
         </is>
@@ -1605,8 +4005,8 @@
           <t>The folder path inside the library, so documents can be separated by folder within one library.</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="F15" s="14" t="inlineStr"/>
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1621,29 +4021,29 @@
           <t>/2026/Q2/Board</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="J15" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr"/>
+      <c r="L15" s="14" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>LibraryName</t>
         </is>
@@ -1653,8 +4053,8 @@
           <t>The display name of the document library holding the file.</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr"/>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr"/>
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1669,7 +4069,7 @@
           <t>Annual Meetings</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
@@ -1679,23 +4079,23 @@
           <t>The deepest level of the drill down.</t>
         </is>
       </c>
-      <c r="L16" s="16" t="inlineStr"/>
+      <c r="L16" s="14" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>LibraryUrl</t>
         </is>
@@ -1705,8 +4105,8 @@
           <t>The web address of the library, for click through.</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr"/>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr"/>
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1721,29 +4121,29 @@
           <t>/sites/edrms-cwrd/AnnualMeet</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr">
+      <c r="J17" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="16" t="inlineStr"/>
+      <c r="L17" s="14" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>LibraryLastActivityDate</t>
         </is>
@@ -1753,8 +4153,8 @@
           <t>The date anything in the library last changed. Used to judge whether a library is still in use.</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr"/>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr"/>
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -1769,7 +4169,7 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="J18" s="14" t="inlineStr">
         <is>
           <t>Microsoft Graph</t>
         </is>
@@ -1779,23 +4179,23 @@
           <t>NEW. Microsoft Graph returns it as lastModifiedDateTime on the drive, from the same call that supplies LibraryCount. Repeated on every document row of that library.</t>
         </is>
       </c>
-      <c r="L18" s="16" t="inlineStr"/>
+      <c r="L18" s="14" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>ListId</t>
         </is>
@@ -1805,8 +4205,8 @@
           <t>The GUID, meaning the system generated identifier, of the SharePoint library. Libraries can be renamed but this does not change, so every library figure groups on it.</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr"/>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr"/>
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>uuid</t>
         </is>
@@ -1821,7 +4221,7 @@
           <t>a869c724-ac4f-4144-8526-69b5aeef3a68</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr">
+      <c r="J19" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
@@ -1831,23 +4231,23 @@
           <t>Verified to match SharePoint's own list GUID, so the join to Graph is safe.</t>
         </is>
       </c>
-      <c r="L19" s="16" t="inlineStr"/>
+      <c r="L19" s="14" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="n">
+      <c r="A20" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>ItemId</t>
         </is>
@@ -1857,8 +4257,8 @@
           <t>The item number SharePoint assigns within a library. Unique inside one library, not across libraries.</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr"/>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr"/>
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -1873,7 +4273,7 @@
           <t>203</t>
         </is>
       </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="J20" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
@@ -1883,23 +4283,23 @@
           <t>With ListId this identifies exactly one item. Together they are the identity of a row.</t>
         </is>
       </c>
-      <c r="L20" s="16" t="inlineStr"/>
+      <c r="L20" s="14" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n">
+      <c r="A21" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>ADBLibraryCategory</t>
         </is>
@@ -1909,12 +4309,12 @@
           <t>The category the library belongs to, used to group records by classification.</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>Retention Label Mapping list</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1929,7 +4329,7 @@
           <t>Common Document Library</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="J21" s="14" t="inlineStr">
         <is>
           <t>SharePoint list</t>
         </is>
@@ -1939,23 +4339,23 @@
           <t>ADBMeta is empty. The same value is maintained today as Library Type in the Retention Label Mapping list.</t>
         </is>
       </c>
-      <c r="L21" s="16" t="inlineStr"/>
+      <c r="L21" s="14" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="n">
+      <c r="A22" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>SiteName</t>
         </is>
@@ -1965,12 +4365,12 @@
           <t>The display name of the SharePoint site holding the file.</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>Site Activity Table</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1985,29 +4385,29 @@
           <t>EDRMS CWRD</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="J22" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="16" t="inlineStr"/>
+      <c r="L22" s="14" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="n">
+      <c r="A23" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>SiteUrl</t>
         </is>
@@ -2017,12 +4417,12 @@
           <t>The web address of the site holding the file. This is the column that joins a document to its site.</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>Site Activity Table</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -2037,7 +4437,7 @@
           <t>https://adb.sharepoint.com/sites/edrms-cwrd</t>
         </is>
       </c>
-      <c r="J23" s="16" t="inlineStr">
+      <c r="J23" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
@@ -2047,23 +4447,23 @@
           <t>The join key behind every department figure. Every existing row already carries it.</t>
         </is>
       </c>
-      <c r="L23" s="16" t="inlineStr"/>
+      <c r="L23" s="14" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="n">
+      <c r="A24" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>SiteCreatedDate</t>
         </is>
@@ -2073,12 +4473,12 @@
           <t>The date the SharePoint site was created. Copied from the Site Activity Table so a document can be filtered by the age of its site without a join.</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>Site Activity Table</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G24" s="14" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -2093,7 +4493,7 @@
           <t>2026-01-18</t>
         </is>
       </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="J24" s="14" t="inlineStr">
         <is>
           <t>Microsoft Graph</t>
         </is>
@@ -2103,23 +4503,23 @@
           <t>NEW.</t>
         </is>
       </c>
-      <c r="L24" s="16" t="inlineStr"/>
+      <c r="L24" s="14" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="n">
+      <c r="A25" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>IsEdrmsCompliant</t>
         </is>
@@ -2129,12 +4529,12 @@
           <t>Whether the site holding this document is an EDRMS compliant site, meaning it has the Declare as Record button.</t>
         </is>
       </c>
-      <c r="F25" s="18" t="inlineStr">
+      <c r="F25" s="16" t="inlineStr">
         <is>
           <t>Site Activity Table</t>
         </is>
       </c>
-      <c r="G25" s="18" t="inlineStr">
+      <c r="G25" s="16" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
@@ -2149,7 +4549,7 @@
           <t>true</t>
         </is>
       </c>
-      <c r="J25" s="19" t="inlineStr">
+      <c r="J25" s="23" t="inlineStr">
         <is>
           <t>NEEDS A DECISION</t>
         </is>
@@ -2159,23 +4559,23 @@
           <t>NEW. Determined by whether the EDRMS app is installed on the site. Defines the population of this whole table.</t>
         </is>
       </c>
-      <c r="L25" s="18" t="inlineStr"/>
+      <c r="L25" s="16" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="n">
+      <c r="A26" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>ADBDepartmentOwner</t>
         </is>
@@ -2185,12 +4585,12 @@
           <t>The department that owns the site holding this document. Inherited from the site rather than set on each document.</t>
         </is>
       </c>
-      <c r="F26" s="18" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>Site Activity Table</t>
         </is>
       </c>
-      <c r="G26" s="18" t="inlineStr">
+      <c r="G26" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -2205,7 +4605,7 @@
           <t>CWRD</t>
         </is>
       </c>
-      <c r="J26" s="19" t="inlineStr">
+      <c r="J26" s="23" t="inlineStr">
         <is>
           <t>NEEDS A DECISION</t>
         </is>
@@ -2215,23 +4615,23 @@
           <t>GAP. The SharePoint column exists and is empty on every row. Arrives from the RAC site mapping, loaded onto the site and inherited through SiteUrl.</t>
         </is>
       </c>
-      <c r="L26" s="18" t="inlineStr"/>
+      <c r="L26" s="16" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="n">
+      <c r="A27" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>IsDeclaredRecord</t>
         </is>
@@ -2241,8 +4641,8 @@
           <t>Whether this document has been formally declared a record. This is the single most important column in the report, because it separates the numerator from the denominator in every rate.</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr"/>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr"/>
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
@@ -2257,7 +4657,7 @@
           <t>true</t>
         </is>
       </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="J27" s="14" t="inlineStr">
         <is>
           <t>Derived at load</t>
         </is>
@@ -2267,23 +4667,23 @@
           <t>NEW but free. Derived at load: true where the document is present in Records, false where the scan found it and Records does not.</t>
         </is>
       </c>
-      <c r="L27" s="16" t="inlineStr"/>
+      <c r="L27" s="14" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="n">
+      <c r="A28" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>CreatedDate</t>
         </is>
@@ -2293,8 +4693,8 @@
           <t>The date and time the user declared the file as a record. Blank for a document that has never been declared.</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr"/>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="F28" s="14" t="inlineStr"/>
+      <c r="G28" s="14" t="inlineStr">
         <is>
           <t>timestamp with time zone</t>
         </is>
@@ -2309,7 +4709,7 @@
           <t>2026-03-12 09:14:00+00</t>
         </is>
       </c>
-      <c r="J28" s="16" t="inlineStr">
+      <c r="J28" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
@@ -2319,23 +4719,23 @@
           <t>Every declaration date filter reads this column. Not the file's own creation date.</t>
         </is>
       </c>
-      <c r="L28" s="16" t="inlineStr"/>
+      <c r="L28" s="14" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="n">
+      <c r="A29" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>CreatedBy</t>
         </is>
@@ -2345,8 +4745,8 @@
           <t>The User Principal Name, meaning the sign-in email address, of the person who declared the record.</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr"/>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="F29" s="14" t="inlineStr"/>
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -2361,29 +4761,29 @@
           <t>jperez@adb.org</t>
         </is>
       </c>
-      <c r="J29" s="16" t="inlineStr">
+      <c r="J29" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr"/>
-      <c r="L29" s="16" t="inlineStr"/>
+      <c r="L29" s="14" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="n">
+      <c r="A30" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="14" t="inlineStr">
         <is>
           <t>DeclarationType</t>
         </is>
@@ -2393,8 +4793,8 @@
           <t>Whether the record was declared individually or through a centralised process, held as a numeric code.</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr"/>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="F30" s="14" t="inlineStr"/>
+      <c r="G30" s="14" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -2409,7 +4809,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J30" s="16" t="inlineStr">
+      <c r="J30" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
@@ -2419,23 +4819,23 @@
           <t>Deployed today as an integer. The code to label mapping needs confirming with the development team.</t>
         </is>
       </c>
-      <c r="L30" s="16" t="inlineStr"/>
+      <c r="L30" s="14" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="n">
+      <c r="A31" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>HasPhysical</t>
         </is>
@@ -2445,8 +4845,8 @@
           <t>Whether a physical paper counterpart of this record exists.</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr"/>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="F31" s="14" t="inlineStr"/>
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
@@ -2461,7 +4861,7 @@
           <t>false</t>
         </is>
       </c>
-      <c r="J31" s="16" t="inlineStr">
+      <c r="J31" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
@@ -2471,23 +4871,23 @@
           <t>Blank rather than false for undeclared documents, since neither answer is known for them.</t>
         </is>
       </c>
-      <c r="L31" s="16" t="inlineStr"/>
+      <c r="L31" s="14" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="n">
+      <c r="A32" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>PhysicalCounterpartRetention</t>
         </is>
@@ -2497,12 +4897,12 @@
           <t>The retention that applies to the physical copy, maintained per library rather than per document.</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F32" s="14" t="inlineStr">
         <is>
           <t>Retention Label Mapping list</t>
         </is>
       </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="G32" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -2517,29 +4917,29 @@
           <t>Long Term</t>
         </is>
       </c>
-      <c r="J32" s="16" t="inlineStr">
+      <c r="J32" s="14" t="inlineStr">
         <is>
           <t>SharePoint list</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr"/>
-      <c r="L32" s="16" t="inlineStr"/>
+      <c r="L32" s="14" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="n">
+      <c r="A33" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>EDRMSRetentionLabel</t>
         </is>
@@ -2549,8 +4949,8 @@
           <t>The retention label applied to the file, which is what determines how long it is kept.</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr"/>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="F33" s="14" t="inlineStr"/>
+      <c r="G33" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -2565,7 +4965,7 @@
           <t>10 years after declaration</t>
         </is>
       </c>
-      <c r="J33" s="16" t="inlineStr">
+      <c r="J33" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
@@ -2575,23 +4975,23 @@
           <t>A record with no label has no disposal date and cannot be scheduled at all.</t>
         </is>
       </c>
-      <c r="L33" s="16" t="inlineStr"/>
+      <c r="L33" s="14" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="n">
+      <c r="A34" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="14" t="inlineStr">
         <is>
           <t>EDRMSDuration</t>
         </is>
@@ -2601,8 +5001,8 @@
           <t>The length of the retention period attached to the label.</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr"/>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="F34" s="14" t="inlineStr"/>
+      <c r="G34" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -2617,7 +5017,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J34" s="16" t="inlineStr">
+      <c r="J34" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
@@ -2627,23 +5027,23 @@
           <t>Stored as text rather than a number so it can hold Permanent alongside 10. Cast before doing arithmetic on it.</t>
         </is>
       </c>
-      <c r="L34" s="16" t="inlineStr"/>
+      <c r="L34" s="14" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="n">
+      <c r="A35" s="13" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C35" s="15" t="inlineStr">
+      <c r="C35" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>EDRMSRetentionLabelApplied</t>
         </is>
@@ -2653,8 +5053,8 @@
           <t>The date and time the retention label was applied to the file.</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr"/>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr"/>
+      <c r="G35" s="14" t="inlineStr">
         <is>
           <t>timestamp with time zone</t>
         </is>
@@ -2669,7 +5069,7 @@
           <t>2026-03-12 09:20:00+00</t>
         </is>
       </c>
-      <c r="J35" s="16" t="inlineStr">
+      <c r="J35" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
@@ -2679,23 +5079,23 @@
           <t>Never use this to date a declaration. A label can be applied to a document that was never declared.</t>
         </is>
       </c>
-      <c r="L35" s="16" t="inlineStr"/>
+      <c r="L35" s="14" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="n">
+      <c r="A36" s="13" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="14" t="inlineStr">
         <is>
           <t>EDRMSDueDateForDisposal</t>
         </is>
@@ -2705,8 +5105,8 @@
           <t>The date the record becomes due for disposal, computed as the label applied date plus the duration.</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr"/>
-      <c r="G36" s="16" t="inlineStr">
+      <c r="F36" s="14" t="inlineStr"/>
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -2721,7 +5121,7 @@
           <t>2036-03-12</t>
         </is>
       </c>
-      <c r="J36" s="16" t="inlineStr">
+      <c r="J36" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
@@ -2731,23 +5131,23 @@
           <t>Already computed in the source database. Records due for disposal is a count over this column and needs nothing new.</t>
         </is>
       </c>
-      <c r="L36" s="16" t="inlineStr"/>
+      <c r="L36" s="14" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="n">
+      <c r="A37" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D37" s="14" t="inlineStr">
         <is>
           <t>RetentionStatus</t>
         </is>
@@ -2757,12 +5157,12 @@
           <t>The retention classification derived from the duration.</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F37" s="14" t="inlineStr">
         <is>
           <t>EDRMSMasters</t>
         </is>
       </c>
-      <c r="G37" s="16" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -2777,29 +5177,29 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J37" s="16" t="inlineStr">
+      <c r="J37" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr"/>
-      <c r="L37" s="16" t="inlineStr"/>
+      <c r="L37" s="14" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="n">
+      <c r="A38" s="13" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C38" s="15" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D38" s="14" t="inlineStr">
         <is>
           <t>SensitivityLabelName</t>
         </is>
@@ -2809,8 +5209,8 @@
           <t>The sensitivity label applied to the file, such as Internal or Confidential.</t>
         </is>
       </c>
-      <c r="F38" s="16" t="inlineStr"/>
-      <c r="G38" s="16" t="inlineStr">
+      <c r="F38" s="14" t="inlineStr"/>
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -2825,7 +5225,7 @@
           <t>Internal</t>
         </is>
       </c>
-      <c r="J38" s="16" t="inlineStr">
+      <c r="J38" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
@@ -2835,23 +5235,23 @@
           <t>Not on any current dashboard. Carried because it is free and the obvious basis for a protection view.</t>
         </is>
       </c>
-      <c r="L38" s="16" t="inlineStr"/>
+      <c r="L38" s="14" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="n">
+      <c r="A39" s="13" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C39" s="15" t="inlineStr">
+      <c r="C39" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D39" s="14" t="inlineStr">
         <is>
           <t>IsDeleted</t>
         </is>
@@ -2861,8 +5261,8 @@
           <t>Soft delete flag. Every count on every dashboard excludes rows where this is true.</t>
         </is>
       </c>
-      <c r="F39" s="16" t="inlineStr"/>
-      <c r="G39" s="16" t="inlineStr">
+      <c r="F39" s="14" t="inlineStr"/>
+      <c r="G39" s="14" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
@@ -2877,7 +5277,7 @@
           <t>false</t>
         </is>
       </c>
-      <c r="J39" s="16" t="inlineStr">
+      <c r="J39" s="14" t="inlineStr">
         <is>
           <t>Derived at load</t>
         </is>
@@ -2887,23 +5287,23 @@
           <t>For undeclared documents, absence from the next scan is the delete signal.</t>
         </is>
       </c>
-      <c r="L39" s="16" t="inlineStr"/>
+      <c r="L39" s="14" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="n">
+      <c r="A40" s="13" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="14" t="inlineStr">
         <is>
           <t>RowLoadedDate</t>
         </is>
@@ -2913,8 +5313,8 @@
           <t>The date and time this row was last written by the refresh job.</t>
         </is>
       </c>
-      <c r="F40" s="16" t="inlineStr"/>
-      <c r="G40" s="16" t="inlineStr">
+      <c r="F40" s="14" t="inlineStr"/>
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>timestamp with time zone</t>
         </is>
@@ -2929,7 +5329,7 @@
           <t>2026-07-27 06:00:00+00</t>
         </is>
       </c>
-      <c r="J40" s="16" t="inlineStr">
+      <c r="J40" s="14" t="inlineStr">
         <is>
           <t>Job generated</t>
         </is>
@@ -2939,7 +5339,7 @@
           <t>NEW. Operational only. Lets a failed or partial refresh be spotted.</t>
         </is>
       </c>
-      <c r="L40" s="16" t="inlineStr"/>
+      <c r="L40" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2950,7 +5350,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2974,96 +5374,96 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>SITE ACTIVITY TABLE</t>
         </is>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>One row per SharePoint site. About 1,057 rows. Exists for the two things a document level table cannot do: count a site that holds no documents, and hold visit and viewer counts that are measured per site and would be nonsense repeated on every document row.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>S/N</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>RELEASE EFFECTIVE</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>DECLARATION TYPE EFFECTIVE</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>COLUMN TITLE</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>REFERENCE TABLES</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>FIELD TYPE</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>FIELD VALUES/ CHOICES</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>WHERE THE VALUE COMES FROM</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="12" t="inlineStr">
         <is>
           <t>REMARKS</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>ADB Comments</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n">
+      <c r="A5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
@@ -3073,8 +5473,8 @@
           <t>Primary key. Uniquely identifies each site row of the snapshot.</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr"/>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr"/>
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>uuid</t>
         </is>
@@ -3089,29 +5489,29 @@
           <t>8c1d47b2-93ae-4f60-b1d5-2e7a6f0c9d31</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>Job generated</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="16" t="inlineStr"/>
+      <c r="L5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>SnapshotDate</t>
         </is>
@@ -3121,8 +5521,8 @@
           <t>The date the refresh job captured this data. The same value on every row of a run.</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr"/>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr"/>
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -3137,7 +5537,7 @@
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>Job generated</t>
         </is>
@@ -3147,23 +5547,23 @@
           <t>NEW.</t>
         </is>
       </c>
-      <c r="L6" s="16" t="inlineStr"/>
+      <c r="L6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>SiteId</t>
         </is>
@@ -3173,8 +5573,8 @@
           <t>The GUID, meaning the system generated identifier, of the SharePoint site. Stable across a rename, unlike the URL.</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>uuid</t>
         </is>
@@ -3189,7 +5589,7 @@
           <t>019adc9b-031d-4edc-b62f-512ed4671947</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t>M365 usage report</t>
         </is>
@@ -3199,23 +5599,23 @@
           <t>NEW. The usage export identifies sites by this and leaves Site URL blank on every row, so the refresh job must merge the export with a Graph site list to connect a GUID to a URL.</t>
         </is>
       </c>
-      <c r="L7" s="16" t="inlineStr"/>
+      <c r="L7" s="14" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>SiteUrl</t>
         </is>
@@ -3225,12 +5625,12 @@
           <t>The web address of the site. This is the column that joins this table to the Utilization Report Table.</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>Utilization Report Table</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -3245,7 +5645,7 @@
           <t>https://adb.sharepoint.com/sites/edrms-cwrd</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
@@ -3255,23 +5655,23 @@
           <t>NOT available from the usage export, where it is empty on all 2,575 rows. Comes from Microsoft Graph, matched to the export on SiteId.</t>
         </is>
       </c>
-      <c r="L8" s="16" t="inlineStr"/>
+      <c r="L8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>SiteName</t>
         </is>
@@ -3281,8 +5681,8 @@
           <t>The display name of the site.</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr"/>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr"/>
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -3297,29 +5697,29 @@
           <t>EDRMS CWRD</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="16" t="inlineStr"/>
+      <c r="L9" s="14" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n">
+      <c r="A10" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>SiteCreatedDate</t>
         </is>
@@ -3329,8 +5729,8 @@
           <t>The date the SharePoint site was created.</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr"/>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr"/>
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -3345,7 +5745,7 @@
           <t>2026-01-18</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>Microsoft Graph</t>
         </is>
@@ -3355,23 +5755,23 @@
           <t>NEW. Microsoft Graph returns it as createdDateTime on every site.</t>
         </is>
       </c>
-      <c r="L10" s="16" t="inlineStr"/>
+      <c r="L10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n">
+      <c r="A11" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>IsEdrmsCompliant</t>
         </is>
@@ -3381,8 +5781,8 @@
           <t>Whether this is an EDRMS compliant site, meaning the Declare as Record button is available in it.</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr"/>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr"/>
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
@@ -3397,7 +5797,7 @@
           <t>true</t>
         </is>
       </c>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t>NEEDS A DECISION</t>
         </is>
@@ -3407,23 +5807,23 @@
           <t>NEW. Determined by whether the EDRMS app is installed on the site. Product ID {B255A2AF-7F63-4A30-966A-5D5FD99F97D7}.</t>
         </is>
       </c>
-      <c r="L11" s="18" t="inlineStr"/>
+      <c r="L11" s="16" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="n">
+      <c r="A12" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>ADBDepartmentOwner</t>
         </is>
@@ -3433,8 +5833,8 @@
           <t>The department that owns this site.</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr"/>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr"/>
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -3449,7 +5849,7 @@
           <t>CWRD</t>
         </is>
       </c>
-      <c r="J12" s="19" t="inlineStr">
+      <c r="J12" s="23" t="inlineStr">
         <is>
           <t>NEEDS A DECISION</t>
         </is>
@@ -3459,23 +5859,23 @@
           <t>GAP. Nothing in SharePoint supplies it. Loaded once from the RAC site mapping, roughly 1,057 rows, and inherited by every document in the site.</t>
         </is>
       </c>
-      <c r="L12" s="18" t="inlineStr"/>
+      <c r="L12" s="16" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>SiteVisits7</t>
         </is>
@@ -3485,8 +5885,8 @@
           <t>The number of page views in the site over the last 7 days.</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr"/>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr"/>
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -3501,7 +5901,7 @@
           <t>412</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="J13" s="14" t="inlineStr">
         <is>
           <t>M365 usage report</t>
         </is>
@@ -3511,23 +5911,23 @@
           <t>NEW. From the Microsoft 365 SharePoint site usage report.</t>
         </is>
       </c>
-      <c r="L13" s="16" t="inlineStr"/>
+      <c r="L13" s="14" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n">
+      <c r="A14" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>SiteVisits30</t>
         </is>
@@ -3537,8 +5937,8 @@
           <t>The number of page views in the site over the last 30 days.</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr"/>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr"/>
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -3553,7 +5953,7 @@
           <t>4812</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="J14" s="14" t="inlineStr">
         <is>
           <t>M365 usage report</t>
         </is>
@@ -3563,23 +5963,23 @@
           <t>NEW. Same report at period='D30'.</t>
         </is>
       </c>
-      <c r="L14" s="16" t="inlineStr"/>
+      <c r="L14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n">
+      <c r="A15" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>SiteVisits90</t>
         </is>
@@ -3589,8 +5989,8 @@
           <t>The number of page views in the site over the last 90 days.</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="F15" s="14" t="inlineStr"/>
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -3605,7 +6005,7 @@
           <t>13240</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="J15" s="14" t="inlineStr">
         <is>
           <t>M365 usage report</t>
         </is>
@@ -3615,23 +6015,23 @@
           <t>NEW. Same report at period='D90'.</t>
         </is>
       </c>
-      <c r="L15" s="16" t="inlineStr"/>
+      <c r="L15" s="14" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>UniqueViewers7</t>
         </is>
@@ -3641,8 +6041,8 @@
           <t>The number of distinct people who opened something in the site over the last 7 days.</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr"/>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr"/>
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -3657,7 +6057,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>Site analytics</t>
         </is>
@@ -3667,23 +6067,23 @@
           <t>NEW. NOT in the usage export, which has no unique viewer column at all. Comes from GET /sites/{id}/analytics/lastSevenDays, the actorCount field. Do not sum across sites to count people: anyone working in three sites is counted three times.</t>
         </is>
       </c>
-      <c r="L16" s="16" t="inlineStr"/>
+      <c r="L16" s="14" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>UniqueViewersAllTime</t>
         </is>
@@ -3693,8 +6093,8 @@
           <t>The number of distinct people who have ever opened something in the site.</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr"/>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr"/>
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -3709,7 +6109,7 @@
           <t>122</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr">
+      <c r="J17" s="14" t="inlineStr">
         <is>
           <t>Site analytics</t>
         </is>
@@ -3719,23 +6119,23 @@
           <t>NEW. Replaces a UniqueViewers30 column that could not be filled: site analytics offers all time and last seven days only, and there is no 30 or 90 day window. Verified against the tenant, which returned actorCount 12 for org_csd_1.4testsite.</t>
         </is>
       </c>
-      <c r="L17" s="16" t="inlineStr"/>
+      <c r="L17" s="14" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>LibraryCount</t>
         </is>
@@ -3745,8 +6145,8 @@
           <t>The number of document libraries in the site.</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr"/>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr"/>
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -3761,7 +6161,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="J18" s="14" t="inlineStr">
         <is>
           <t>Microsoft Graph</t>
         </is>
@@ -3771,23 +6171,23 @@
           <t>NEW. Microsoft Graph, GET /sites/{id}/drives, counted.</t>
         </is>
       </c>
-      <c r="L18" s="16" t="inlineStr"/>
+      <c r="L18" s="14" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>LastActivityDate</t>
         </is>
@@ -3797,8 +6197,8 @@
           <t>The date anything in the site was last touched.</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr"/>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr"/>
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -3813,7 +6213,7 @@
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr">
+      <c r="J19" s="14" t="inlineStr">
         <is>
           <t>M365 usage report</t>
         </is>
@@ -3823,23 +6223,23 @@
           <t>NEW. A site with no activity for 90 days is reported as inactive. The threshold is applied in the report, not stored here.</t>
         </is>
       </c>
-      <c r="L19" s="16" t="inlineStr"/>
+      <c r="L19" s="14" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="n">
+      <c r="A20" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>StorageUsed</t>
         </is>
@@ -3849,8 +6249,8 @@
           <t>The storage consumed by the site, in bytes.</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr"/>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr"/>
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
@@ -3865,7 +6265,7 @@
           <t>13636370432</t>
         </is>
       </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="J20" s="14" t="inlineStr">
         <is>
           <t>M365 usage report</t>
         </is>
@@ -3875,23 +6275,23 @@
           <t>NEW. Includes version history, so it reads higher than the sum of FileSize. Expected, not an error.</t>
         </is>
       </c>
-      <c r="L20" s="16" t="inlineStr"/>
+      <c r="L20" s="14" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n">
+      <c r="A21" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>SiteOwner</t>
         </is>
@@ -3901,8 +6301,8 @@
           <t>The User Principal Name of the primary site administrator, meaning who to contact about a site that has gone quiet.</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr"/>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr"/>
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -3917,7 +6317,7 @@
           <t>jperez@adb.org</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="J21" s="14" t="inlineStr">
         <is>
           <t>M365 usage report</t>
         </is>
@@ -3927,23 +6327,23 @@
           <t>NEW. Usage export, Owner Principal Name. Verified: 1,899 of 1,918 live sites carry one, so 19 have no owner at all.</t>
         </is>
       </c>
-      <c r="L21" s="16" t="inlineStr"/>
+      <c r="L21" s="14" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="n">
+      <c r="A22" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>ProjectEndDate</t>
         </is>
@@ -3953,12 +6353,12 @@
           <t>The project end date recorded against the site.</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>ADBSites</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -3973,7 +6373,7 @@
           <t>2027-12-31</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="J22" s="14" t="inlineStr">
         <is>
           <t>EDRMS database</t>
         </is>
@@ -3983,23 +6383,23 @@
           <t>Already exists and is populated. The obvious basis for a site closure view.</t>
         </is>
       </c>
-      <c r="L22" s="16" t="inlineStr"/>
+      <c r="L22" s="14" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="n">
+      <c r="A23" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>IsDeleted</t>
         </is>
@@ -4009,8 +6409,8 @@
           <t>Soft delete flag. Closed sites stay in the table so historical figures do not change.</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr"/>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr"/>
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
@@ -4025,7 +6425,7 @@
           <t>false</t>
         </is>
       </c>
-      <c r="J23" s="16" t="inlineStr">
+      <c r="J23" s="14" t="inlineStr">
         <is>
           <t>Derived at load</t>
         </is>
@@ -4035,23 +6435,23 @@
           <t>A site missing from the next export is the delete signal.</t>
         </is>
       </c>
-      <c r="L23" s="16" t="inlineStr"/>
+      <c r="L23" s="14" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="n">
+      <c r="A24" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>RowLoadedDate</t>
         </is>
@@ -4061,8 +6461,8 @@
           <t>The date and time this row was last written.</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr"/>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="F24" s="14" t="inlineStr"/>
+      <c r="G24" s="14" t="inlineStr">
         <is>
           <t>timestamp with time zone</t>
         </is>
@@ -4077,7 +6477,7 @@
           <t>2026-07-27 06:00:00+00</t>
         </is>
       </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="J24" s="14" t="inlineStr">
         <is>
           <t>Job generated</t>
         </is>
@@ -4087,7 +6487,7 @@
           <t>NEW. Operational only.</t>
         </is>
       </c>
-      <c r="L24" s="16" t="inlineStr"/>
+      <c r="L24" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4098,7 +6498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4122,96 +6522,96 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>USER ACTIVITY TABLE</t>
         </is>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>One row per person who used SharePoint in the window. About 9,400 rows. Exists because Total EDRMS Users counts people, and a person working in three sites appears in three rows of the Site Activity Table, so summing UniqueViewers30 overstates headcount.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>S/N</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>RELEASE EFFECTIVE</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>DECLARATION TYPE EFFECTIVE</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>COLUMN TITLE</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>REFERENCE TABLES</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>FIELD TYPE</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>FIELD VALUES/ CHOICES</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>WHERE THE VALUE COMES FROM</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="12" t="inlineStr">
         <is>
           <t>REMARKS</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>ADB Comments</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n">
+      <c r="A5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
@@ -4221,8 +6621,8 @@
           <t>Primary key. Uniquely identifies each person row of the snapshot.</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr"/>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr"/>
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>uuid</t>
         </is>
@@ -4237,29 +6637,29 @@
           <t>b47f2e0a-5c93-41d8-8a16-7f3d05e6b8c2</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>Job generated</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="16" t="inlineStr"/>
+      <c r="L5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>SnapshotDate</t>
         </is>
@@ -4269,8 +6669,8 @@
           <t>The date the refresh job captured this data.</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr"/>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr"/>
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -4285,7 +6685,7 @@
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>Job generated</t>
         </is>
@@ -4295,23 +6695,23 @@
           <t>NEW.</t>
         </is>
       </c>
-      <c r="L6" s="16" t="inlineStr"/>
+      <c r="L6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>UserPrincipalName</t>
         </is>
@@ -4321,8 +6721,8 @@
           <t>The User Principal Name, meaning the sign-in email address, of a person who used SharePoint in the window. Counting distinct values of this column is the entire purpose of the table.</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -4337,7 +6737,7 @@
           <t>jperez@adb.org</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t>M365 usage report</t>
         </is>
@@ -4347,23 +6747,23 @@
           <t>NEW. This is why the table exists: people cannot be counted from a table of sites. **Monthly active users is NOT the row count**: the export lists every licensed user, active or not. Verified on the tenant, where 30 rows held only 8 people who viewed or edited anything. Count rows where ViewedOrEditedFileCount is above zero.</t>
         </is>
       </c>
-      <c r="L7" s="16" t="inlineStr"/>
+      <c r="L7" s="14" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>DisplayName</t>
         </is>
@@ -4373,8 +6773,8 @@
           <t>The person's display name, for readability when the list is inspected.</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr"/>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr"/>
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -4389,7 +6789,7 @@
           <t>J Perez</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>Microsoft Graph</t>
         </is>
@@ -4399,23 +6799,23 @@
           <t>NEW. NOT in the activity export, which carries User Principal Name and no display name. Needs a separate Graph call to /users, and it is cosmetic, so drop it if that call is not worth making.</t>
         </is>
       </c>
-      <c r="L8" s="16" t="inlineStr"/>
+      <c r="L8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>LastActivityDate</t>
         </is>
@@ -4425,8 +6825,8 @@
           <t>The date of the person's most recent SharePoint activity.</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr"/>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr"/>
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -4441,7 +6841,7 @@
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>M365 usage report</t>
         </is>
@@ -4451,23 +6851,23 @@
           <t>NEW. Filter on this to count active users over 7 or 30 days.</t>
         </is>
       </c>
-      <c r="L9" s="16" t="inlineStr"/>
+      <c r="L9" s="14" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n">
+      <c r="A10" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>ViewedOrEditedFileCount</t>
         </is>
@@ -4477,8 +6877,8 @@
           <t>The number of files the person viewed or edited during the window.</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr"/>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr"/>
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -4493,7 +6893,7 @@
           <t>42</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>M365 usage report</t>
         </is>
@@ -4503,23 +6903,23 @@
           <t>NEW. Separates heavy users from someone who opened one document, and is the obvious basis for an adoption view.</t>
         </is>
       </c>
-      <c r="L10" s="16" t="inlineStr"/>
+      <c r="L10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n">
+      <c r="A11" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>RowLoadedDate</t>
         </is>
@@ -4529,8 +6929,8 @@
           <t>The date and time this row was last written.</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr"/>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr"/>
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>timestamp with time zone</t>
         </is>
@@ -4545,7 +6945,7 @@
           <t>2026-07-27 06:00:00+00</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t>Job generated</t>
         </is>
@@ -4555,7 +6955,7 @@
           <t>NEW. Operational only.</t>
         </is>
       </c>
-      <c r="L11" s="16" t="inlineStr"/>
+      <c r="L11" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4566,7 +6966,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4590,96 +6990,96 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>FILE PLAN TABLE</t>
         </is>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>One row per term in the institutional file plan. Exists because the file plan is the taxonomy that classifies content, so its terms are neither documents nor sites nor people and none of the other three tables can hold them.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>S/N</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>RELEASE EFFECTIVE</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>DECLARATION TYPE EFFECTIVE</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>COLUMN TITLE</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>REFERENCE TABLES</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>FIELD TYPE</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>FIELD VALUES/ CHOICES</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>WHERE THE VALUE COMES FROM</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="12" t="inlineStr">
         <is>
           <t>REMARKS</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>ADB Comments</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n">
+      <c r="A5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
@@ -4689,8 +7089,8 @@
           <t>Primary key. Uniquely identifies each term row of the snapshot.</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr"/>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr"/>
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>uuid</t>
         </is>
@@ -4705,29 +7105,29 @@
           <t>e05b8c31-7d42-4a96-b3f8-1c9e4a70d582</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>Job generated</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="16" t="inlineStr"/>
+      <c r="L5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>SnapshotDate</t>
         </is>
@@ -4737,8 +7137,8 @@
           <t>The date the refresh job captured this data.</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr"/>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr"/>
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -4753,7 +7153,7 @@
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>Job generated</t>
         </is>
@@ -4763,23 +7163,23 @@
           <t>NEW.</t>
         </is>
       </c>
-      <c r="L6" s="16" t="inlineStr"/>
+      <c r="L6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>TermId</t>
         </is>
@@ -4789,8 +7189,8 @@
           <t>The GUID, meaning the system generated identifier, of the term. Stable across a rename, so counts do not jump when somebody edits a label.</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>uuid</t>
         </is>
@@ -4805,7 +7205,7 @@
           <t>6f2c1a48-9b30-4e75-8d21-c4a7e0f39a41</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t>Term store</t>
         </is>
@@ -4815,23 +7215,23 @@
           <t>NEW.</t>
         </is>
       </c>
-      <c r="L7" s="16" t="inlineStr"/>
+      <c r="L7" s="14" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>TermName</t>
         </is>
@@ -4841,8 +7241,8 @@
           <t>The label of the term as it appears in the term store.</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr"/>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr"/>
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -4857,7 +7257,7 @@
           <t>Procurement Planning</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>Term store</t>
         </is>
@@ -4867,23 +7267,23 @@
           <t>NEW.</t>
         </is>
       </c>
-      <c r="L8" s="16" t="inlineStr"/>
+      <c r="L8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>TermSetName</t>
         </is>
@@ -4893,8 +7293,8 @@
           <t>The term set the term belongs to.</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr"/>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr"/>
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -4909,7 +7309,7 @@
           <t>Procurement</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>Term store</t>
         </is>
@@ -4919,23 +7319,23 @@
           <t>NEW.</t>
         </is>
       </c>
-      <c r="L9" s="16" t="inlineStr"/>
+      <c r="L9" s="14" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="n">
+      <c r="A10" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>CategoryName</t>
         </is>
@@ -4945,8 +7345,8 @@
           <t>The top level term group the term sits under, which is what the report groups by.</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr"/>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr"/>
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -4961,7 +7361,7 @@
           <t>ADB</t>
         </is>
       </c>
-      <c r="J10" s="19" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>NEEDS A DECISION</t>
         </is>
@@ -4971,23 +7371,23 @@
           <t>NEW. UNVERIFIED. The five categories in the requirement do not exist in the tenant's term store. See the Structure sheet.</t>
         </is>
       </c>
-      <c r="L10" s="18" t="inlineStr"/>
+      <c r="L10" s="16" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n">
+      <c r="A11" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Depth</t>
         </is>
@@ -4997,8 +7397,8 @@
           <t>How many levels below the term set the term sits. A term directly under a term set is 1.</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr"/>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr"/>
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -5013,7 +7413,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t>Term store</t>
         </is>
@@ -5023,23 +7423,23 @@
           <t>NEW. Recorded while walking the tree at no extra cost, and it answers how deep the plan actually runs.</t>
         </is>
       </c>
-      <c r="L11" s="16" t="inlineStr"/>
+      <c r="L11" s="14" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>2026.4</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>RowLoadedDate</t>
         </is>
@@ -5049,8 +7449,8 @@
           <t>The date and time this row was last written.</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr"/>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr"/>
+      <c r="G12" s="14" t="inlineStr">
         <is>
           <t>timestamp with time zone</t>
         </is>
@@ -5065,7 +7465,7 @@
           <t>2026-07-27 06:00:00+00</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>Job generated</t>
         </is>
@@ -5075,7 +7475,7 @@
           <t>NEW. Operational only.</t>
         </is>
       </c>
-      <c r="L12" s="16" t="inlineStr"/>
+      <c r="L12" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/EDRMS_Utilization_Report_Database_Design_v1.xlsx
+++ b/EDRMS_Utilization_Report_Database_Design_v1.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -676,10 +676,10 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr"/>
     </row>
-    <row r="17" ht="46" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Thresholds are not stored. LastActivityDate is a fact; "inactive after 90 days" is a judgement made in the report. Keeping judgements out of the database means changing 90 to 120 costs one edit in Power BI and no change to the job, the tables or the refresh.</t>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>HISTORY IS KEPT ON THREE TABLES OUT OF FOUR</t>
         </is>
       </c>
     </row>
@@ -689,17 +689,17 @@
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Nothing writes into these tables from Microsoft or AvePoint. Neither can push to PostgreSQL. A scheduled job pulls from Microsoft Graph, the Microsoft 365 usage reports and the term store, and writes the rows. Power BI then reads only these tables and never contacts SharePoint.</t>
+          <t>Site Activity, User Activity and File Plan are RETAINED. Every weekly run inserts a new set of rows rather than replacing the last, and SnapshotDate is part of the primary key. That is what makes a date range possible on usage figures, which Microsoft supplies only as pre-aggregated windows with no row per visit to filter. It also supplies every trend view in the requirements. The cost is small: about 55,000 site rows and 490,000 user rows a year.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>TWO THINGS THAT ARE NOT SETTLED</t>
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>The Utilization Report Table is REPLACED. At 3.47 million rows a week, a year of history would be 180 million rows, and it is not needed because every document row already carries its own dates: CreatedDate, FileCreatedDate, FileModifiedDate and EDRMSDueDateForDisposal all support a free date range today with no history at all.</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
     <row r="23" ht="46" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>ADBDepartmentOwner has no source. The SharePoint column exists and is empty on every row. It arrives as a one time mapping of site to department from RAC, loaded onto the Site Activity Table, and every document inherits it through SiteUrl. Confirmed feasible by the development team on 10 August 2026, with no migration required.</t>
+          <t>The earliest selectable date is the first run. History that was never captured cannot be recovered, which is why this decision could not wait: every week it is deferred is a week the report can never report on.</t>
         </is>
       </c>
     </row>
@@ -719,29 +719,89 @@
     <row r="25" ht="46" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>Two rules the queries must follow. Reports read the LATEST snapshot by default, or 1,057 compliant sites silently becomes 55,000 after a year. And a date range sums SiteVisits7 across the weeks in the range, never SiteVisits30 or SiteVisits90: consecutive 7 day windows tile exactly, while 30 and 90 day windows overlap and would count most days several times over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="46" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Thresholds are not stored. LastActivityDate is a fact; "inactive after 90 days" is a judgement made in the report. Keeping judgements out of the database means changing 90 to 120 costs one edit in Power BI and no change to the job, the tables or the refresh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29" ht="46" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Nothing writes into these tables from Microsoft or AvePoint. Neither can push to PostgreSQL. A scheduled job pulls from Microsoft Graph, the Microsoft 365 usage reports and the term store, and writes the rows. Power BI then reads only these tables and never contacts SharePoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>TWO THINGS THAT ARE NOT SETTLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33" ht="46" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>ADBDepartmentOwner has no source. The SharePoint column exists and is empty on every row. It arrives as a one time mapping of site to department from RAC, loaded onto the Site Activity Table, and every document inherits it through SiteUrl. Confirmed feasible by the development team on 10 August 2026, with no migration required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="46" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t>The File Plan Table is unverified. The five categories named in the requirement do not exist in the tenant term store, whose groups are ADB, ADB Exchange, ADB Test and similar. The Purview file plan holds 53 retention labels as a flat list with no such categories either. Where the institutional file plan actually lives is a question for the client before this table is built.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="28">
     <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A24:D24"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3564,7 +3624,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>NEW. One value per run. A dashboard is only as current as this date.</t>
+          <t>NEW. One value per run. A dashboard is only as current as this date. THIS TABLE IS REPLACED, NOT RETAINED, unlike the other three: at 3.47 million rows a week a year of history would be 180 million rows, and it is not needed, because every document row already carries its own dates.</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr"/>
@@ -5544,7 +5604,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>NEW.</t>
+          <t>NEW. PART OF THE PRIMARY KEY. This table is RETAINED: every weekly run inserts a new set of rows rather than replacing the last, so a site has one row per week. Reports read the most recent snapshot unless a date range is applied. The earliest selectable date is the first run, because history that was never captured cannot be recovered.</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr"/>
@@ -5908,7 +5968,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>NEW. From the Microsoft 365 SharePoint site usage report.</t>
+          <t>NEW. From the Microsoft 365 SharePoint site usage report. THIS IS THE COLUMN A DATE RANGE SUMS. Consecutive weekly snapshots of a 7 day window do not overlap, so adding them across the weeks in a range gives the visits for that range correctly.</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr"/>
@@ -5960,7 +6020,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>NEW. Same report at period='D30'.</t>
+          <t>NEW. Same report at period='D30'. NEVER SUM THIS ACROSS SNAPSHOTS. Weekly runs of a 30 day window overlap heavily, so adding four of them counts most days four times. Point in time reading only.</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr"/>
@@ -6012,7 +6072,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>NEW. Same report at period='D90'.</t>
+          <t>NEW. Same report at period='D90'. Never sum across snapshots, for the same reason as the 30 day figure.</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr"/>
@@ -6692,7 +6752,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>NEW.</t>
+          <t>NEW. PART OF THE PRIMARY KEY. Retained, one row per person per week. Counting distinct UserPrincipalName across the snapshots in a range gives distinct people over that range, which is the only correct way to answer it: viewer counts cannot be added up, because the same person appearing in four weeks would be counted four times.</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr"/>
@@ -7160,7 +7220,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>NEW.</t>
+          <t>NEW. PART OF THE PRIMARY KEY. Retained, so the file plan can be seen as it stood at any past refresh, which is what shows a taxonomy growing.</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr"/>

--- a/EDRMS_Utilization_Report_Database_Design_v1.xlsx
+++ b/EDRMS_Utilization_Report_Database_Design_v1.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
     <row r="25" ht="46" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Two rules the queries must follow. Reports read the LATEST snapshot by default, or 1,057 compliant sites silently becomes 55,000 after a year. And a date range sums SiteVisits7 across the weeks in the range, never SiteVisits30 or SiteVisits90: consecutive 7 day windows tile exactly, while 30 and 90 day windows overlap and would count most days several times over.</t>
+          <t>Three rules the queries must follow. Reports read the LATEST snapshot by default, or 1,057 compliant sites silently becomes 55,000 after a year. A date range sums SiteVisits7 across the weeks in the range, never SiteVisits30 or SiteVisits90: consecutive 7 day windows tile exactly, while 30 and 90 day windows overlap and would count most days several times over. And the range must be matched on ReportRefreshDate, not SnapshotDate.</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
     <row r="27" ht="46" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Thresholds are not stored. LastActivityDate is a fact; "inactive after 90 days" is a judgement made in the report. Keeping judgements out of the database means changing 90 to 120 costs one edit in Power BI and no change to the job, the tables or the refresh.</t>
+          <t>That last one is easy to get wrong. SnapshotDate is when the job ran. ReportRefreshDate is the last day Microsoft actually measured, and it lags: an export taken on 12 Aug 2026 carried figures as at 10 Aug. The lag varies, so tiling on the job date makes consecutive weekly windows overlap or leave gaps, and a range total comes out wrong while looking entirely reasonable. Store both dates and tile on the refresh date. The window a row covers is ReportRefreshDate minus the period plus one, through ReportRefreshDate.</t>
         </is>
       </c>
     </row>
@@ -739,27 +739,27 @@
     <row r="29" ht="46" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Nothing writes into these tables from Microsoft or AvePoint. Neither can push to PostgreSQL. A scheduled job pulls from Microsoft Graph, the Microsoft 365 usage reports and the term store, and writes the rows. Power BI then reads only these tables and never contacts SharePoint.</t>
+          <t>Thresholds are not stored. LastActivityDate is a fact; "inactive after 90 days" is a judgement made in the report. Keeping judgements out of the database means changing 90 to 120 costs one edit in Power BI and no change to the job, the tables or the refresh.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr"/>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>TWO THINGS THAT ARE NOT SETTLED</t>
+    <row r="31" ht="46" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Nothing writes into these tables from Microsoft or AvePoint. Neither can push to PostgreSQL. A scheduled job pulls from Microsoft Graph, the Microsoft 365 usage reports and the term store, and writes the rows. Power BI then reads only these tables and never contacts SharePoint.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr"/>
     </row>
-    <row r="33" ht="46" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>ADBDepartmentOwner has no source. The SharePoint column exists and is empty on every row. It arrives as a one time mapping of site to department from RAC, loaded onto the Site Activity Table, and every document inherits it through SiteUrl. Confirmed feasible by the development team on 10 August 2026, with no migration required.</t>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>TWO THINGS THAT ARE NOT SETTLED</t>
         </is>
       </c>
     </row>
@@ -769,12 +769,22 @@
     <row r="35" ht="46" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>ADBDepartmentOwner has no source. The SharePoint column exists and is empty on every row. It arrives as a one time mapping of site to department from RAC, loaded onto the Site Activity Table, and every document inherits it through SiteUrl. Confirmed feasible by the development team on 10 August 2026, with no migration required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="46" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
           <t>The File Plan Table is unverified. The five categories named in the requirement do not exist in the tenant term store, whose groups are ADB, ADB Exchange, ADB Test and similar. The Purview file plan holds 53 retention labels as a flat list with no such categories either. Where the institutional file plan actually lives is a question for the client before this table is built.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="30">
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A22:D22"/>
@@ -791,9 +801,11 @@
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A12:D12"/>
@@ -833,7 +845,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>71 columns across four tables. 65 have a source that exists today. 6 do not, and those are shaded red on the table sheets. Nothing else is customised: every other column is either read from a system, computed from columns already present, or written by the job itself.</t>
+          <t>73 columns across four tables. 67 have a source that exists today. 6 do not, and those are shaded red on the table sheets. Nothing else is customised: every other column is either read from a system, computed from columns already present, or written by the job itself.</t>
         </is>
       </c>
     </row>
@@ -906,7 +918,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -915,7 +927,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>SiteActivity.SiteId, SiteActivity.SiteVisits7, SiteActivity.SiteVisits30, SiteActivity.SiteVisits90, SiteActivity.LastActivityDate, SiteActivity.StorageUsed, SiteActivity.SiteOwner, UserActivity.UserPrincipalName, UserActivity.LastActivityDate, UserActivity.ViewedOrEditedFileCount</t>
+          <t>SiteActivity.SiteId, SiteActivity.ReportRefreshDate, SiteActivity.SiteVisits7, SiteActivity.SiteVisits30, SiteActivity.SiteVisits90, SiteActivity.LastActivityDate, SiteActivity.StorageUsed, SiteActivity.SiteOwner, UserActivity.ReportRefreshDate, UserActivity.UserPrincipalName, UserActivity.LastActivityDate, UserActivity.ViewedOrEditedFileCount</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2502,12 +2514,12 @@
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>SiteVisits7</t>
+          <t>ReportRefreshDate</t>
         </is>
       </c>
       <c r="D49" s="18" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>date</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
@@ -2517,7 +2529,7 @@
       </c>
       <c r="F49" s="18" t="inlineStr">
         <is>
-          <t>Page View Count</t>
+          <t>Report Refresh Date</t>
         </is>
       </c>
       <c r="G49" s="20" t="inlineStr">
@@ -2527,7 +2539,7 @@
       </c>
       <c r="H49" s="19" t="inlineStr">
         <is>
-          <t>Site usage CSV at period D7</t>
+          <t>Both CSVs, 12 Aug 2026. Value 2026-08-10 on every row, with Report Period 30, so the window is 12 Jul to 10 Aug</t>
         </is>
       </c>
       <c r="I49" s="19" t="inlineStr"/>
@@ -2544,7 +2556,7 @@
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>SiteVisits30</t>
+          <t>SiteVisits7</t>
         </is>
       </c>
       <c r="D50" s="18" t="inlineStr">
@@ -2569,7 +2581,7 @@
       </c>
       <c r="H50" s="19" t="inlineStr">
         <is>
-          <t>Site usage CSV, 12 Aug 2026, period 30</t>
+          <t>Site usage CSV at period D7</t>
         </is>
       </c>
       <c r="I50" s="19" t="inlineStr"/>
@@ -2586,7 +2598,7 @@
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>SiteVisits90</t>
+          <t>SiteVisits30</t>
         </is>
       </c>
       <c r="D51" s="18" t="inlineStr">
@@ -2611,155 +2623,155 @@
       </c>
       <c r="H51" s="19" t="inlineStr">
         <is>
-          <t>Site usage CSV at period D90</t>
+          <t>Site usage CSV, 12 Aug 2026, period 30</t>
         </is>
       </c>
       <c r="I51" s="19" t="inlineStr"/>
       <c r="J51" s="17" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="13" t="n">
+      <c r="A52" s="17" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B52" s="18" t="inlineStr">
         <is>
           <t>SiteActivity</t>
         </is>
       </c>
-      <c r="C52" s="14" t="inlineStr">
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>SiteVisits90</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E52" s="19" t="inlineStr">
+        <is>
+          <t>One of the two usage CSVs</t>
+        </is>
+      </c>
+      <c r="F52" s="18" t="inlineStr">
+        <is>
+          <t>Page View Count</t>
+        </is>
+      </c>
+      <c r="G52" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H52" s="19" t="inlineStr">
+        <is>
+          <t>Site usage CSV at period D90</t>
+        </is>
+      </c>
+      <c r="I52" s="19" t="inlineStr"/>
+      <c r="J52" s="17" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>SiteActivity</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
         <is>
           <t>UniqueViewers7</t>
         </is>
       </c>
-      <c r="D52" s="14" t="inlineStr">
+      <c r="D53" s="14" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>GET /sites/{id}/analytics/{allTime|lastSevenDays}</t>
         </is>
       </c>
-      <c r="F52" s="14" t="inlineStr"/>
-      <c r="G52" s="13" t="inlineStr"/>
-      <c r="H52" s="4" t="inlineStr"/>
-      <c r="I52" s="4" t="inlineStr"/>
-      <c r="J52" s="13" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="17" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="18" t="inlineStr">
+      <c r="F53" s="14" t="inlineStr"/>
+      <c r="G53" s="13" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" s="4" t="inlineStr"/>
+      <c r="J53" s="13" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
         <is>
           <t>SiteActivity</t>
         </is>
       </c>
-      <c r="C53" s="18" t="inlineStr">
+      <c r="C54" s="18" t="inlineStr">
         <is>
           <t>UniqueViewersAllTime</t>
         </is>
       </c>
-      <c r="D53" s="18" t="inlineStr">
+      <c r="D54" s="18" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E53" s="19" t="inlineStr">
+      <c r="E54" s="19" t="inlineStr">
         <is>
           <t>GET /sites/{id}/analytics/{allTime|lastSevenDays}</t>
         </is>
       </c>
-      <c r="F53" s="18" t="inlineStr">
+      <c r="F54" s="18" t="inlineStr">
         <is>
           <t>actorCount</t>
         </is>
       </c>
-      <c r="G53" s="20" t="inlineStr">
+      <c r="G54" s="20" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H53" s="19" t="inlineStr">
+      <c r="H54" s="19" t="inlineStr">
         <is>
           <t>GET /sites/{id}/analytics/allTime returned actorCount 12</t>
         </is>
       </c>
-      <c r="I53" s="19" t="inlineStr"/>
-      <c r="J53" s="17" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="I54" s="19" t="inlineStr"/>
+      <c r="J54" s="17" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>SiteActivity</t>
         </is>
       </c>
-      <c r="C54" s="14" t="inlineStr">
+      <c r="C55" s="14" t="inlineStr">
         <is>
           <t>LibraryCount</t>
         </is>
       </c>
-      <c r="D54" s="14" t="inlineStr">
+      <c r="D55" s="14" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>A Graph call. See the REMARKS column on the table sheet</t>
         </is>
       </c>
-      <c r="F54" s="14" t="inlineStr"/>
-      <c r="G54" s="13" t="inlineStr"/>
-      <c r="H54" s="4" t="inlineStr"/>
-      <c r="I54" s="4" t="inlineStr"/>
-      <c r="J54" s="13" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="17" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="18" t="inlineStr">
-        <is>
-          <t>SiteActivity</t>
-        </is>
-      </c>
-      <c r="C55" s="18" t="inlineStr">
-        <is>
-          <t>LastActivityDate</t>
-        </is>
-      </c>
-      <c r="D55" s="18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="E55" s="19" t="inlineStr">
-        <is>
-          <t>One of the two usage CSVs</t>
-        </is>
-      </c>
-      <c r="F55" s="18" t="inlineStr">
-        <is>
-          <t>Last Activity Date</t>
-        </is>
-      </c>
-      <c r="G55" s="20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H55" s="19" t="inlineStr">
-        <is>
-          <t>Site usage CSV. 381 of 1,918 live sites carry one</t>
-        </is>
-      </c>
-      <c r="I55" s="19" t="inlineStr"/>
-      <c r="J55" s="17" t="inlineStr"/>
+      <c r="F55" s="14" t="inlineStr"/>
+      <c r="G55" s="13" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr"/>
+      <c r="J55" s="13" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="17" t="n">
@@ -2772,12 +2784,12 @@
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>StorageUsed</t>
+          <t>LastActivityDate</t>
         </is>
       </c>
       <c r="D56" s="18" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>date</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr">
@@ -2787,7 +2799,7 @@
       </c>
       <c r="F56" s="18" t="inlineStr">
         <is>
-          <t>Storage Used (Byte)</t>
+          <t>Last Activity Date</t>
         </is>
       </c>
       <c r="G56" s="20" t="inlineStr">
@@ -2797,7 +2809,7 @@
       </c>
       <c r="H56" s="19" t="inlineStr">
         <is>
-          <t>Site usage CSV. Sums to 142.4 GB</t>
+          <t>Site usage CSV. 381 of 1,918 live sites carry one</t>
         </is>
       </c>
       <c r="I56" s="19" t="inlineStr"/>
@@ -2814,12 +2826,12 @@
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>SiteOwner</t>
+          <t>StorageUsed</t>
         </is>
       </c>
       <c r="D57" s="18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="E57" s="19" t="inlineStr">
@@ -2829,7 +2841,7 @@
       </c>
       <c r="F57" s="18" t="inlineStr">
         <is>
-          <t>Owner Principal Name</t>
+          <t>Storage Used (Byte)</t>
         </is>
       </c>
       <c r="G57" s="20" t="inlineStr">
@@ -2839,41 +2851,53 @@
       </c>
       <c r="H57" s="19" t="inlineStr">
         <is>
-          <t>Site usage CSV. 1,899 of 1,918 have one, 19 do not</t>
+          <t>Site usage CSV. Sums to 142.4 GB</t>
         </is>
       </c>
       <c r="I57" s="19" t="inlineStr"/>
       <c r="J57" s="17" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="13" t="n">
+      <c r="A58" s="17" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B58" s="18" t="inlineStr">
         <is>
           <t>SiteActivity</t>
         </is>
       </c>
-      <c r="C58" s="14" t="inlineStr">
-        <is>
-          <t>ProjectEndDate</t>
-        </is>
-      </c>
-      <c r="D58" s="14" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>Query public."Records" or ADBSites in drm-npr</t>
-        </is>
-      </c>
-      <c r="F58" s="14" t="inlineStr"/>
-      <c r="G58" s="13" t="inlineStr"/>
-      <c r="H58" s="4" t="inlineStr"/>
-      <c r="I58" s="4" t="inlineStr"/>
-      <c r="J58" s="13" t="inlineStr"/>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>SiteOwner</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E58" s="19" t="inlineStr">
+        <is>
+          <t>One of the two usage CSVs</t>
+        </is>
+      </c>
+      <c r="F58" s="18" t="inlineStr">
+        <is>
+          <t>Owner Principal Name</t>
+        </is>
+      </c>
+      <c r="G58" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H58" s="19" t="inlineStr">
+        <is>
+          <t>Site usage CSV. 1,899 of 1,918 have one, 19 do not</t>
+        </is>
+      </c>
+      <c r="I58" s="19" t="inlineStr"/>
+      <c r="J58" s="17" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="13" t="n">
@@ -2886,17 +2910,17 @@
       </c>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>IsDeleted</t>
+          <t>ProjectEndDate</t>
         </is>
       </c>
       <c r="D59" s="14" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>date</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Nothing to test. Computed by the job</t>
+          <t>Query public."Records" or ADBSites in drm-npr</t>
         </is>
       </c>
       <c r="F59" s="14" t="inlineStr"/>
@@ -2916,17 +2940,17 @@
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>RowLoadedDate</t>
+          <t>IsDeleted</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>timestamp with time zone</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Nothing to test. Written by the job</t>
+          <t>Nothing to test. Computed by the job</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr"/>
@@ -2941,17 +2965,17 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>UserActivity</t>
+          <t>SiteActivity</t>
         </is>
       </c>
       <c r="C61" s="14" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>RowLoadedDate</t>
         </is>
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>timestamp with time zone</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -2976,12 +3000,12 @@
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>SnapshotDate</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -2996,76 +3020,76 @@
       <c r="J62" s="13" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="17" t="n">
+      <c r="A63" s="13" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="18" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>UserActivity</t>
         </is>
       </c>
-      <c r="C63" s="18" t="inlineStr">
-        <is>
-          <t>UserPrincipalName</t>
-        </is>
-      </c>
-      <c r="D63" s="18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E63" s="19" t="inlineStr">
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>SnapshotDate</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to test. Written by the job</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr"/>
+      <c r="G63" s="13" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr"/>
+      <c r="I63" s="4" t="inlineStr"/>
+      <c r="J63" s="13" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>UserActivity</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>ReportRefreshDate</t>
+        </is>
+      </c>
+      <c r="D64" s="18" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E64" s="19" t="inlineStr">
         <is>
           <t>One of the two usage CSVs</t>
         </is>
       </c>
-      <c r="F63" s="18" t="inlineStr">
-        <is>
-          <t>User Principal Name</t>
-        </is>
-      </c>
-      <c r="G63" s="20" t="inlineStr">
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>Report Refresh Date</t>
+        </is>
+      </c>
+      <c r="G64" s="20" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H63" s="19" t="inlineStr">
-        <is>
-          <t>Activity CSV, 12 Aug 2026, 30 rows</t>
-        </is>
-      </c>
-      <c r="I63" s="19" t="inlineStr"/>
-      <c r="J63" s="17" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="14" t="inlineStr">
-        <is>
-          <t>UserActivity</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="inlineStr">
-        <is>
-          <t>DisplayName</t>
-        </is>
-      </c>
-      <c r="D64" s="14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>A Graph call. See the REMARKS column on the table sheet</t>
-        </is>
-      </c>
-      <c r="F64" s="14" t="inlineStr"/>
-      <c r="G64" s="13" t="inlineStr"/>
-      <c r="H64" s="4" t="inlineStr"/>
-      <c r="I64" s="4" t="inlineStr"/>
-      <c r="J64" s="13" t="inlineStr"/>
+      <c r="H64" s="19" t="inlineStr">
+        <is>
+          <t>Same column in the activity export, same 2026-08-10 and period 30</t>
+        </is>
+      </c>
+      <c r="I64" s="19" t="inlineStr"/>
+      <c r="J64" s="17" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="17" t="n">
@@ -3078,12 +3102,12 @@
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>LastActivityDate</t>
+          <t>UserPrincipalName</t>
         </is>
       </c>
       <c r="D65" s="18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
@@ -3093,7 +3117,7 @@
       </c>
       <c r="F65" s="18" t="inlineStr">
         <is>
-          <t>Last Activity Date</t>
+          <t>User Principal Name</t>
         </is>
       </c>
       <c r="G65" s="20" t="inlineStr">
@@ -3103,113 +3127,125 @@
       </c>
       <c r="H65" s="19" t="inlineStr">
         <is>
-          <t>Activity CSV. 25 of 30 rows carry one</t>
+          <t>Activity CSV, 12 Aug 2026, 30 rows</t>
         </is>
       </c>
       <c r="I65" s="19" t="inlineStr"/>
       <c r="J65" s="17" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="17" t="n">
+      <c r="A66" s="13" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="18" t="inlineStr">
+      <c r="B66" s="14" t="inlineStr">
         <is>
           <t>UserActivity</t>
         </is>
       </c>
-      <c r="C66" s="18" t="inlineStr">
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>A Graph call. See the REMARKS column on the table sheet</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="inlineStr"/>
+      <c r="G66" s="13" t="inlineStr"/>
+      <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr"/>
+      <c r="J66" s="13" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>UserActivity</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t>LastActivityDate</t>
+        </is>
+      </c>
+      <c r="D67" s="18" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E67" s="19" t="inlineStr">
+        <is>
+          <t>One of the two usage CSVs</t>
+        </is>
+      </c>
+      <c r="F67" s="18" t="inlineStr">
+        <is>
+          <t>Last Activity Date</t>
+        </is>
+      </c>
+      <c r="G67" s="20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H67" s="19" t="inlineStr">
+        <is>
+          <t>Activity CSV. 25 of 30 rows carry one</t>
+        </is>
+      </c>
+      <c r="I67" s="19" t="inlineStr"/>
+      <c r="J67" s="17" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>UserActivity</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
         <is>
           <t>ViewedOrEditedFileCount</t>
         </is>
       </c>
-      <c r="D66" s="18" t="inlineStr">
+      <c r="D68" s="18" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E66" s="19" t="inlineStr">
+      <c r="E68" s="19" t="inlineStr">
         <is>
           <t>One of the two usage CSVs</t>
         </is>
       </c>
-      <c r="F66" s="18" t="inlineStr">
+      <c r="F68" s="18" t="inlineStr">
         <is>
           <t>Viewed Or Edited File Count</t>
         </is>
       </c>
-      <c r="G66" s="20" t="inlineStr">
+      <c r="G68" s="20" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H66" s="19" t="inlineStr">
+      <c r="H68" s="19" t="inlineStr">
         <is>
           <t>Activity CSV. Only 8 of 30 are above zero, which is the real active user count</t>
         </is>
       </c>
-      <c r="I66" s="19" t="inlineStr"/>
-      <c r="J66" s="17" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="13" t="n">
-        <v>63</v>
-      </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>UserActivity</t>
-        </is>
-      </c>
-      <c r="C67" s="14" t="inlineStr">
-        <is>
-          <t>RowLoadedDate</t>
-        </is>
-      </c>
-      <c r="D67" s="14" t="inlineStr">
-        <is>
-          <t>timestamp with time zone</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>Nothing to test. Written by the job</t>
-        </is>
-      </c>
-      <c r="F67" s="14" t="inlineStr"/>
-      <c r="G67" s="13" t="inlineStr"/>
-      <c r="H67" s="4" t="inlineStr"/>
-      <c r="I67" s="4" t="inlineStr"/>
-      <c r="J67" s="13" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="13" t="n">
-        <v>64</v>
-      </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>FilePlan</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="D68" s="14" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>Nothing to test. Written by the job</t>
-        </is>
-      </c>
-      <c r="F68" s="14" t="inlineStr"/>
-      <c r="G68" s="13" t="inlineStr"/>
-      <c r="H68" s="4" t="inlineStr"/>
-      <c r="I68" s="4" t="inlineStr"/>
-      <c r="J68" s="13" t="inlineStr"/>
+      <c r="I68" s="19" t="inlineStr"/>
+      <c r="J68" s="17" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="13" t="n">
@@ -3217,17 +3253,17 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>FilePlan</t>
+          <t>UserActivity</t>
         </is>
       </c>
       <c r="C69" s="14" t="inlineStr">
         <is>
-          <t>SnapshotDate</t>
+          <t>RowLoadedDate</t>
         </is>
       </c>
       <c r="D69" s="14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>timestamp with time zone</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -3252,7 +3288,7 @@
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>TermId</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
@@ -3262,7 +3298,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>SharePoint admin centre, Content services, Term store</t>
+          <t>Nothing to test. Written by the job</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr"/>
@@ -3282,17 +3318,17 @@
       </c>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>TermName</t>
+          <t>SnapshotDate</t>
         </is>
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>SharePoint admin centre, Content services, Term store</t>
+          <t>Nothing to test. Written by the job</t>
         </is>
       </c>
       <c r="F71" s="14" t="inlineStr"/>
@@ -3312,12 +3348,12 @@
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>TermSetName</t>
+          <t>TermId</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -3332,34 +3368,34 @@
       <c r="J72" s="13" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="15" t="n">
+      <c r="A73" s="13" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="16" t="inlineStr">
+      <c r="B73" s="14" t="inlineStr">
         <is>
           <t>FilePlan</t>
         </is>
       </c>
-      <c r="C73" s="16" t="inlineStr">
-        <is>
-          <t>CategoryName</t>
-        </is>
-      </c>
-      <c r="D73" s="16" t="inlineStr">
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>TermName</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E73" s="11" t="inlineStr">
-        <is>
-          <t>Nothing to test. Somebody must supply a list or write a rule</t>
-        </is>
-      </c>
-      <c r="F73" s="16" t="inlineStr"/>
-      <c r="G73" s="15" t="inlineStr"/>
-      <c r="H73" s="11" t="inlineStr"/>
-      <c r="I73" s="11" t="inlineStr"/>
-      <c r="J73" s="15" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>SharePoint admin centre, Content services, Term store</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="inlineStr"/>
+      <c r="G73" s="13" t="inlineStr"/>
+      <c r="H73" s="4" t="inlineStr"/>
+      <c r="I73" s="4" t="inlineStr"/>
+      <c r="J73" s="13" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="13" t="n">
@@ -3372,12 +3408,12 @@
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Depth</t>
+          <t>TermSetName</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -3392,34 +3428,94 @@
       <c r="J74" s="13" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="13" t="n">
+      <c r="A75" s="15" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="14" t="inlineStr">
+      <c r="B75" s="16" t="inlineStr">
         <is>
           <t>FilePlan</t>
         </is>
       </c>
-      <c r="C75" s="14" t="inlineStr">
+      <c r="C75" s="16" t="inlineStr">
+        <is>
+          <t>CategoryName</t>
+        </is>
+      </c>
+      <c r="D75" s="16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>Nothing to test. Somebody must supply a list or write a rule</t>
+        </is>
+      </c>
+      <c r="F75" s="16" t="inlineStr"/>
+      <c r="G75" s="15" t="inlineStr"/>
+      <c r="H75" s="11" t="inlineStr"/>
+      <c r="I75" s="11" t="inlineStr"/>
+      <c r="J75" s="15" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>FilePlan</t>
+        </is>
+      </c>
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>Depth</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>SharePoint admin centre, Content services, Term store</t>
+        </is>
+      </c>
+      <c r="F76" s="14" t="inlineStr"/>
+      <c r="G76" s="13" t="inlineStr"/>
+      <c r="H76" s="4" t="inlineStr"/>
+      <c r="I76" s="4" t="inlineStr"/>
+      <c r="J76" s="13" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="n">
+        <v>73</v>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>FilePlan</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
         <is>
           <t>RowLoadedDate</t>
         </is>
       </c>
-      <c r="D75" s="14" t="inlineStr">
+      <c r="D77" s="14" t="inlineStr">
         <is>
           <t>timestamp with time zone</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>Nothing to test. Written by the job</t>
         </is>
       </c>
-      <c r="F75" s="14" t="inlineStr"/>
-      <c r="G75" s="13" t="inlineStr"/>
-      <c r="H75" s="4" t="inlineStr"/>
-      <c r="I75" s="4" t="inlineStr"/>
-      <c r="J75" s="13" t="inlineStr"/>
+      <c r="F77" s="14" t="inlineStr"/>
+      <c r="G77" s="13" t="inlineStr"/>
+      <c r="H77" s="4" t="inlineStr"/>
+      <c r="I77" s="4" t="inlineStr"/>
+      <c r="J77" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5416,7 +5512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.9" customWidth="1" min="1" max="1"/>
@@ -5937,18 +6033,18 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>SiteVisits7</t>
+          <t>ReportRefreshDate</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>The number of page views in the site over the last 7 days.</t>
+          <t>The last day Microsoft's usage figures actually cover. Every count on this row is measured over the window ending on this date, not on the date the job ran.</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr"/>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>date</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -5958,7 +6054,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="J13" s="14" t="inlineStr">
@@ -5968,7 +6064,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>NEW. From the Microsoft 365 SharePoint site usage report. THIS IS THE COLUMN A DATE RANGE SUMS. Consecutive weekly snapshots of a 7 day window do not overlap, so adding them across the weeks in a range gives the visits for that range correctly.</t>
+          <t>NEW. Report Refresh Date in both usage exports. WITHOUT THIS COLUMN THE VISIT COUNTS HAVE NO DATES ATTACHED. Microsoft refreshes on its own schedule and lags: an export taken on 12 Aug 2026 carried figures as at 10 Aug, a two day lag, and the lag varies. A date range must tile on THIS column, never on SnapshotDate, or consecutive weekly windows overlap or leave gaps and the total is quietly wrong. The window covered is ReportRefreshDate minus the period plus one, through ReportRefreshDate.</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr"/>
@@ -5989,12 +6085,12 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>SiteVisits30</t>
+          <t>SiteVisits7</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>The number of page views in the site over the last 30 days.</t>
+          <t>The number of page views in the site over the last 7 days.</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr"/>
@@ -6010,7 +6106,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>412</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
@@ -6020,7 +6116,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>NEW. Same report at period='D30'. NEVER SUM THIS ACROSS SNAPSHOTS. Weekly runs of a 30 day window overlap heavily, so adding four of them counts most days four times. Point in time reading only.</t>
+          <t>NEW. From the Microsoft 365 SharePoint site usage report. THIS IS THE COLUMN A DATE RANGE SUMS. Consecutive weekly snapshots of a 7 day window do not overlap, so adding them across the weeks in a range gives the visits for that range correctly.</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr"/>
@@ -6041,12 +6137,12 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>SiteVisits90</t>
+          <t>SiteVisits30</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>The number of page views in the site over the last 90 days.</t>
+          <t>The number of page views in the site over the last 30 days.</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr"/>
@@ -6062,7 +6158,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>13240</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="J15" s="14" t="inlineStr">
@@ -6072,7 +6168,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>NEW. Same report at period='D90'. Never sum across snapshots, for the same reason as the 30 day figure.</t>
+          <t>NEW. Same report at period='D30'. NEVER SUM THIS ACROSS SNAPSHOTS. Weekly runs of a 30 day window overlap heavily, so adding four of them counts most days four times. Point in time reading only.</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr"/>
@@ -6093,12 +6189,12 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>UniqueViewers7</t>
+          <t>SiteVisits90</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>The number of distinct people who opened something in the site over the last 7 days.</t>
+          <t>The number of page views in the site over the last 90 days.</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr"/>
@@ -6114,17 +6210,17 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>Site analytics</t>
+          <t>M365 usage report</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>NEW. NOT in the usage export, which has no unique viewer column at all. Comes from GET /sites/{id}/analytics/lastSevenDays, the actorCount field. Do not sum across sites to count people: anyone working in three sites is counted three times.</t>
+          <t>NEW. Same report at period='D90'. Never sum across snapshots, for the same reason as the 30 day figure.</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr"/>
@@ -6145,12 +6241,12 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>UniqueViewersAllTime</t>
+          <t>UniqueViewers7</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>The number of distinct people who have ever opened something in the site.</t>
+          <t>The number of distinct people who opened something in the site over the last 7 days.</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr"/>
@@ -6166,7 +6262,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J17" s="14" t="inlineStr">
@@ -6176,7 +6272,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>NEW. Replaces a UniqueViewers30 column that could not be filled: site analytics offers all time and last seven days only, and there is no 30 or 90 day window. Verified against the tenant, which returned actorCount 12 for org_csd_1.4testsite.</t>
+          <t>NEW. NOT in the usage export, which has no unique viewer column at all. Comes from GET /sites/{id}/analytics/lastSevenDays, the actorCount field. Do not sum across sites to count people: anyone working in three sites is counted three times.</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr"/>
@@ -6197,12 +6293,12 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>LibraryCount</t>
+          <t>UniqueViewersAllTime</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>The number of document libraries in the site.</t>
+          <t>The number of distinct people who have ever opened something in the site.</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr"/>
@@ -6218,17 +6314,17 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>122</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>Microsoft Graph</t>
+          <t>Site analytics</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>NEW. Microsoft Graph, GET /sites/{id}/drives, counted.</t>
+          <t>NEW. Replaces a UniqueViewers30 column that could not be filled: site analytics offers all time and last seven days only, and there is no 30 or 90 day window. Verified against the tenant, which returned actorCount 12 for org_csd_1.4testsite.</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr"/>
@@ -6249,18 +6345,18 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>LastActivityDate</t>
+          <t>LibraryCount</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>The date anything in the site was last touched.</t>
+          <t>The number of document libraries in the site.</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -6270,17 +6366,17 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J19" s="14" t="inlineStr">
         <is>
-          <t>M365 usage report</t>
+          <t>Microsoft Graph</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>NEW. A site with no activity for 90 days is reported as inactive. The threshold is applied in the report, not stored here.</t>
+          <t>NEW. Microsoft Graph, GET /sites/{id}/drives, counted.</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr"/>
@@ -6301,18 +6397,18 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>StorageUsed</t>
+          <t>LastActivityDate</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>The storage consumed by the site, in bytes.</t>
+          <t>The date anything in the site was last touched.</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>date</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -6322,7 +6418,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>13636370432</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J20" s="14" t="inlineStr">
@@ -6332,7 +6428,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>NEW. Includes version history, so it reads higher than the sum of FileSize. Expected, not an error.</t>
+          <t>NEW. A site with no activity for 90 days is reported as inactive. The threshold is applied in the report, not stored here.</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr"/>
@@ -6353,28 +6449,28 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>SiteOwner</t>
+          <t>StorageUsed</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>The User Principal Name of the primary site administrator, meaning who to contact about a site that has gone quiet.</t>
+          <t>The storage consumed by the site, in bytes.</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Valid ADB UPN</t>
+          <t>System generated</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>jperez@adb.org</t>
+          <t>13636370432</t>
         </is>
       </c>
       <c r="J21" s="14" t="inlineStr">
@@ -6384,7 +6480,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>NEW. Usage export, Owner Principal Name. Verified: 1,899 of 1,918 live sites carry one, so 19 have no owner at all.</t>
+          <t>NEW. Includes version history, so it reads higher than the sum of FileSize. Expected, not an error.</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr"/>
@@ -6405,42 +6501,38 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>ProjectEndDate</t>
+          <t>SiteOwner</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>The project end date recorded against the site.</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="inlineStr">
-        <is>
-          <t>ADBSites</t>
-        </is>
-      </c>
+          <t>The User Principal Name of the primary site administrator, meaning who to contact about a site that has gone quiet.</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>System generated</t>
+          <t>Valid ADB UPN</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>jperez@adb.org</t>
         </is>
       </c>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>EDRMS database</t>
+          <t>M365 usage report</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>Already exists and is populated. The obvious basis for a site closure view.</t>
+          <t>NEW. Usage export, Owner Principal Name. Verified: 1,899 of 1,918 live sites carry one, so 19 have no owner at all.</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr"/>
@@ -6461,38 +6553,42 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>IsDeleted</t>
+          <t>ProjectEndDate</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Soft delete flag. Closed sites stay in the table so historical figures do not change.</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr"/>
+          <t>The project end date recorded against the site.</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>ADBSites</t>
+        </is>
+      </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>date</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>true / false</t>
+          <t>System generated</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>2027-12-31</t>
         </is>
       </c>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>Derived at load</t>
+          <t>EDRMS database</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>A site missing from the next export is the delete signal.</t>
+          <t>Already exists and is populated. The obvious basis for a site closure view.</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr"/>
@@ -6513,41 +6609,93 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>RowLoadedDate</t>
+          <t>IsDeleted</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>The date and time this row was last written.</t>
+          <t>Soft delete flag. Closed sites stay in the table so historical figures do not change.</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>true / false</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Derived at load</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>A site missing from the next export is the delete signal.</t>
+        </is>
+      </c>
+      <c r="L24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>RowLoadedDate</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>The date and time this row was last written.</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr"/>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
           <t>timestamp with time zone</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>System generated</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>2026-07-27 06:00:00+00</t>
         </is>
       </c>
-      <c r="J24" s="14" t="inlineStr">
+      <c r="J25" s="14" t="inlineStr">
         <is>
           <t>Job generated</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>NEW. Operational only.</t>
         </is>
       </c>
-      <c r="L24" s="14" t="inlineStr"/>
+      <c r="L25" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6564,7 +6712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.9" customWidth="1" min="1" max="1"/>
@@ -6773,28 +6921,28 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>UserPrincipalName</t>
+          <t>ReportRefreshDate</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>The User Principal Name, meaning the sign-in email address, of a person who used SharePoint in the window. Counting distinct values of this column is the entire purpose of the table.</t>
+          <t>The last day Microsoft's usage figures actually cover. Every count on this row is measured over the window ending on this date, not on the date the job ran.</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr"/>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Valid ADB UPN</t>
+          <t>System generated</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>jperez@adb.org</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="J7" s="14" t="inlineStr">
@@ -6804,7 +6952,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>NEW. This is why the table exists: people cannot be counted from a table of sites. **Monthly active users is NOT the row count**: the export lists every licensed user, active or not. Verified on the tenant, where 30 rows held only 8 people who viewed or edited anything. Count rows where ViewedOrEditedFileCount is above zero.</t>
+          <t>NEW. Report Refresh Date in both usage exports. WITHOUT THIS COLUMN THE VISIT COUNTS HAVE NO DATES ATTACHED. Microsoft refreshes on its own schedule and lags: an export taken on 12 Aug 2026 carried figures as at 10 Aug, a two day lag, and the lag varies. A date range must tile on THIS column, never on SnapshotDate, or consecutive weekly windows overlap or leave gaps and the total is quietly wrong. The window covered is ReportRefreshDate minus the period plus one, through ReportRefreshDate.</t>
         </is>
       </c>
       <c r="L7" s="14" t="inlineStr"/>
@@ -6825,12 +6973,12 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>DisplayName</t>
+          <t>UserPrincipalName</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>The person's display name, for readability when the list is inspected.</t>
+          <t>The User Principal Name, meaning the sign-in email address, of a person who used SharePoint in the window. Counting distinct values of this column is the entire purpose of the table.</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr"/>
@@ -6841,22 +6989,22 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Free text</t>
+          <t>Valid ADB UPN</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>J Perez</t>
+          <t>jperez@adb.org</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>Microsoft Graph</t>
+          <t>M365 usage report</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>NEW. NOT in the activity export, which carries User Principal Name and no display name. Needs a separate Graph call to /users, and it is cosmetic, so drop it if that call is not worth making.</t>
+          <t>NEW. This is why the table exists: people cannot be counted from a table of sites. **Monthly active users is NOT the row count**: the export lists every licensed user, active or not. Verified on the tenant, where 30 rows held only 8 people who viewed or edited anything. Count rows where ViewedOrEditedFileCount is above zero.</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr"/>
@@ -6877,38 +7025,38 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>LastActivityDate</t>
+          <t>DisplayName</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>The date of the person's most recent SharePoint activity.</t>
+          <t>The person's display name, for readability when the list is inspected.</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr"/>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>System generated</t>
+          <t>Free text</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>J Perez</t>
         </is>
       </c>
       <c r="J9" s="14" t="inlineStr">
         <is>
-          <t>M365 usage report</t>
+          <t>Microsoft Graph</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>NEW. Filter on this to count active users over 7 or 30 days.</t>
+          <t>NEW. NOT in the activity export, which carries User Principal Name and no display name. Needs a separate Graph call to /users, and it is cosmetic, so drop it if that call is not worth making.</t>
         </is>
       </c>
       <c r="L9" s="14" t="inlineStr"/>
@@ -6929,18 +7077,18 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>ViewedOrEditedFileCount</t>
+          <t>LastActivityDate</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>The number of files the person viewed or edited during the window.</t>
+          <t>The date of the person's most recent SharePoint activity.</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr"/>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>date</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -6950,7 +7098,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
@@ -6960,7 +7108,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>NEW. Separates heavy users from someone who opened one document, and is the obvious basis for an adoption view.</t>
+          <t>NEW. Filter on this to count active users over 7 or 30 days.</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr"/>
@@ -6981,41 +7129,93 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>RowLoadedDate</t>
+          <t>ViewedOrEditedFileCount</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>The date and time this row was last written.</t>
+          <t>The number of files the person viewed or edited during the window.</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr"/>
       <c r="G11" s="14" t="inlineStr">
         <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>System generated</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>M365 usage report</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>NEW. Separates heavy users from someone who opened one document, and is the obvious basis for an adoption view.</t>
+        </is>
+      </c>
+      <c r="L11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>2026.4</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>RowLoadedDate</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>The date and time this row was last written.</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr"/>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
           <t>timestamp with time zone</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>System generated</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>2026-07-27 06:00:00+00</t>
         </is>
       </c>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>Job generated</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>NEW. Operational only.</t>
         </is>
       </c>
-      <c r="L11" s="14" t="inlineStr"/>
+      <c r="L12" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
